--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -267,7 +267,7 @@
         <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>157.0</v>
+        <v>163.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -293,7 +293,7 @@
         <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>356.0</v>
+        <v>362.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -319,7 +319,7 @@
         <v>53</v>
       </c>
       <c r="F4" t="n">
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -345,7 +345,7 @@
         <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>318.0</v>
+        <v>326.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -371,7 +371,7 @@
         <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>753.0</v>
+        <v>762.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -605,7 +605,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>465.0</v>
+        <v>469.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -657,7 +657,7 @@
         <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>467.0</v>
+        <v>481.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
@@ -683,10 +683,10 @@
         <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>3852.0</v>
+        <v>3876.0</v>
       </c>
       <c r="G18" t="n">
-        <v>109.0</v>
+        <v>112.0</v>
       </c>
       <c r="H18" t="n">
         <v>422.0</v>
@@ -709,7 +709,7 @@
         <v>53</v>
       </c>
       <c r="F19" t="n">
-        <v>1746.0</v>
+        <v>1750.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -761,10 +761,10 @@
         <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>656.0</v>
+        <v>662.0</v>
       </c>
       <c r="G21" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="H21" t="n">
         <v>0.0</v>
@@ -1073,7 +1073,7 @@
         <v>53</v>
       </c>
       <c r="F33" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1099,7 +1099,7 @@
         <v>53</v>
       </c>
       <c r="F34" t="n">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1359,7 +1359,7 @@
         <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>1165.0</v>
+        <v>1168.0</v>
       </c>
       <c r="G44" t="n">
         <v>1.0</v>
@@ -1385,7 +1385,7 @@
         <v>53</v>
       </c>
       <c r="F45" t="n">
-        <v>635.0</v>
+        <v>647.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1411,7 +1411,7 @@
         <v>53</v>
       </c>
       <c r="F46" t="n">
-        <v>392.0</v>
+        <v>403.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1463,7 +1463,7 @@
         <v>53</v>
       </c>
       <c r="F48" t="n">
-        <v>115.0</v>
+        <v>119.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1905,7 +1905,7 @@
         <v>54</v>
       </c>
       <c r="F65" t="n">
-        <v>29.0</v>
+        <v>34.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1931,7 +1931,7 @@
         <v>54</v>
       </c>
       <c r="F66" t="n">
-        <v>280.0</v>
+        <v>286.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1957,7 +1957,7 @@
         <v>54</v>
       </c>
       <c r="F67" t="n">
-        <v>2294.0</v>
+        <v>2299.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1983,7 +1983,7 @@
         <v>54</v>
       </c>
       <c r="F68" t="n">
-        <v>629.0</v>
+        <v>632.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2009,7 +2009,7 @@
         <v>54</v>
       </c>
       <c r="F69" t="n">
-        <v>158.0</v>
+        <v>161.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2321,7 +2321,7 @@
         <v>54</v>
       </c>
       <c r="F81" t="n">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2347,7 +2347,7 @@
         <v>54</v>
       </c>
       <c r="F82" t="n">
-        <v>2910.0</v>
+        <v>2922.0</v>
       </c>
       <c r="G82" t="n">
         <v>2.0</v>
@@ -2373,7 +2373,7 @@
         <v>54</v>
       </c>
       <c r="F83" t="n">
-        <v>4494.0</v>
+        <v>4508.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2945,7 +2945,7 @@
         <v>54</v>
       </c>
       <c r="F105" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -397,10 +397,10 @@
         <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>1259.0</v>
+        <v>1260.0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H7" t="n">
         <v>0.0</v>
@@ -501,7 +501,7 @@
         <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>551.0</v>
+        <v>555.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>10975.0</v>
+        <v>10977.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>3525.0</v>
+        <v>3532.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -839,10 +839,10 @@
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>6777.0</v>
+        <v>6791.0</v>
       </c>
       <c r="G24" t="n">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="H24" t="n">
         <v>261.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>4675.0</v>
+        <v>4676.0</v>
       </c>
       <c r="G28" t="n">
         <v>37.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>2827.0</v>
+        <v>2829.0</v>
       </c>
       <c r="G60" t="n">
         <v>8.0</v>
@@ -2139,7 +2139,7 @@
         <v>54</v>
       </c>
       <c r="F74" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -2165,7 +2165,7 @@
         <v>54</v>
       </c>
       <c r="F75" t="n">
-        <v>1109.0</v>
+        <v>1113.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2607,7 +2607,7 @@
         <v>54</v>
       </c>
       <c r="F92" t="n">
-        <v>356.0</v>
+        <v>358.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -3257,7 +3257,7 @@
         <v>54</v>
       </c>
       <c r="F117" t="n">
-        <v>12970.0</v>
+        <v>12985.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>617.0</v>
+        <v>619.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -3335,7 +3335,7 @@
         <v>54</v>
       </c>
       <c r="F120" t="n">
-        <v>1166.0</v>
+        <v>1167.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -293,7 +293,7 @@
         <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>362.0</v>
+        <v>364.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -423,7 +423,7 @@
         <v>53</v>
       </c>
       <c r="F8" t="n">
-        <v>764.0</v>
+        <v>767.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1445.0</v>
+        <v>1449.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -553,7 +553,7 @@
         <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>175.0</v>
+        <v>179.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -657,7 +657,7 @@
         <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>481.0</v>
+        <v>486.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
@@ -683,7 +683,7 @@
         <v>53</v>
       </c>
       <c r="F18" t="n">
-        <v>3876.0</v>
+        <v>3878.0</v>
       </c>
       <c r="G18" t="n">
         <v>112.0</v>
@@ -709,7 +709,7 @@
         <v>53</v>
       </c>
       <c r="F19" t="n">
-        <v>1750.0</v>
+        <v>1752.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>3532.0</v>
+        <v>3535.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -865,7 +865,7 @@
         <v>53</v>
       </c>
       <c r="F25" t="n">
-        <v>3649.0</v>
+        <v>3658.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -969,7 +969,7 @@
         <v>53</v>
       </c>
       <c r="F29" t="n">
-        <v>1685.0</v>
+        <v>1687.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1385,7 +1385,7 @@
         <v>53</v>
       </c>
       <c r="F45" t="n">
-        <v>647.0</v>
+        <v>649.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1411,7 +1411,7 @@
         <v>53</v>
       </c>
       <c r="F46" t="n">
-        <v>403.0</v>
+        <v>405.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1541,7 +1541,7 @@
         <v>53</v>
       </c>
       <c r="F51" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1619,7 +1619,7 @@
         <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>1599.0</v>
+        <v>1605.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1645,7 +1645,7 @@
         <v>53</v>
       </c>
       <c r="F55" t="n">
-        <v>756.0</v>
+        <v>758.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1749,7 +1749,7 @@
         <v>53</v>
       </c>
       <c r="F59" t="n">
-        <v>1221.0</v>
+        <v>1222.0</v>
       </c>
       <c r="G59" t="n">
         <v>5.0</v>
@@ -1931,7 +1931,7 @@
         <v>54</v>
       </c>
       <c r="F66" t="n">
-        <v>286.0</v>
+        <v>292.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1957,7 +1957,7 @@
         <v>54</v>
       </c>
       <c r="F67" t="n">
-        <v>2299.0</v>
+        <v>2314.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1983,7 +1983,7 @@
         <v>54</v>
       </c>
       <c r="F68" t="n">
-        <v>632.0</v>
+        <v>635.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2087,7 +2087,7 @@
         <v>54</v>
       </c>
       <c r="F72" t="n">
-        <v>2271.0</v>
+        <v>2281.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2165,7 +2165,7 @@
         <v>54</v>
       </c>
       <c r="F75" t="n">
-        <v>1113.0</v>
+        <v>1120.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2321,7 +2321,7 @@
         <v>54</v>
       </c>
       <c r="F81" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2347,7 +2347,7 @@
         <v>54</v>
       </c>
       <c r="F82" t="n">
-        <v>2922.0</v>
+        <v>2929.0</v>
       </c>
       <c r="G82" t="n">
         <v>2.0</v>
@@ -2373,7 +2373,7 @@
         <v>54</v>
       </c>
       <c r="F83" t="n">
-        <v>4508.0</v>
+        <v>4511.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2945,7 +2945,7 @@
         <v>54</v>
       </c>
       <c r="F105" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -3023,7 +3023,7 @@
         <v>54</v>
       </c>
       <c r="F108" t="n">
-        <v>295.0</v>
+        <v>297.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3075,7 +3075,7 @@
         <v>54</v>
       </c>
       <c r="F110" t="n">
-        <v>4002.0</v>
+        <v>4003.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3101,7 +3101,7 @@
         <v>54</v>
       </c>
       <c r="F111" t="n">
-        <v>7953.0</v>
+        <v>7956.0</v>
       </c>
       <c r="G111" t="n">
         <v>1.0</v>
@@ -3205,7 +3205,7 @@
         <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="G115" t="n">
         <v>1.0</v>
@@ -3257,7 +3257,7 @@
         <v>54</v>
       </c>
       <c r="F117" t="n">
-        <v>12985.0</v>
+        <v>12997.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -605,7 +605,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -631,7 +631,7 @@
         <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>3535.0</v>
+        <v>3545.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -839,7 +839,7 @@
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>6791.0</v>
+        <v>6794.0</v>
       </c>
       <c r="G24" t="n">
         <v>47.0</v>
@@ -1079,7 +1079,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="34">
@@ -1313,7 +1313,7 @@
         <v>0.0</v>
       </c>
       <c r="H42" t="n">
-        <v>161.0</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="43">
@@ -1333,7 +1333,7 @@
         <v>53</v>
       </c>
       <c r="F43" t="n">
-        <v>1407.0</v>
+        <v>1411.0</v>
       </c>
       <c r="G43" t="n">
         <v>2.0</v>
@@ -1359,7 +1359,7 @@
         <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>1168.0</v>
+        <v>1175.0</v>
       </c>
       <c r="G44" t="n">
         <v>1.0</v>
@@ -1671,7 +1671,7 @@
         <v>53</v>
       </c>
       <c r="F56" t="n">
-        <v>1759.0</v>
+        <v>1760.0</v>
       </c>
       <c r="G56" t="n">
         <v>4.0</v>
@@ -1749,7 +1749,7 @@
         <v>53</v>
       </c>
       <c r="F59" t="n">
-        <v>1222.0</v>
+        <v>1224.0</v>
       </c>
       <c r="G59" t="n">
         <v>5.0</v>
@@ -2607,7 +2607,7 @@
         <v>54</v>
       </c>
       <c r="F92" t="n">
-        <v>358.0</v>
+        <v>359.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -475,7 +475,7 @@
         <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>1884.0</v>
+        <v>1885.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -501,7 +501,7 @@
         <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>555.0</v>
+        <v>557.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -553,7 +553,7 @@
         <v>53</v>
       </c>
       <c r="F13" t="n">
-        <v>179.0</v>
+        <v>181.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -605,7 +605,7 @@
         <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>471.0</v>
+        <v>478.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>3545.0</v>
+        <v>3552.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -839,7 +839,7 @@
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>6794.0</v>
+        <v>6796.0</v>
       </c>
       <c r="G24" t="n">
         <v>47.0</v>
@@ -891,7 +891,7 @@
         <v>53</v>
       </c>
       <c r="F26" t="n">
-        <v>6260.0</v>
+        <v>6264.0</v>
       </c>
       <c r="G26" t="n">
         <v>8.0</v>
@@ -917,7 +917,7 @@
         <v>53</v>
       </c>
       <c r="F27" t="n">
-        <v>1755.0</v>
+        <v>1758.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>4676.0</v>
+        <v>4681.0</v>
       </c>
       <c r="G28" t="n">
         <v>37.0</v>
@@ -969,7 +969,7 @@
         <v>53</v>
       </c>
       <c r="F29" t="n">
-        <v>1687.0</v>
+        <v>1690.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1203,7 +1203,7 @@
         <v>53</v>
       </c>
       <c r="F38" t="n">
-        <v>2352.0</v>
+        <v>2353.0</v>
       </c>
       <c r="G38" t="n">
         <v>13.0</v>
@@ -1229,7 +1229,7 @@
         <v>53</v>
       </c>
       <c r="F39" t="n">
-        <v>1735.0</v>
+        <v>1737.0</v>
       </c>
       <c r="G39" t="n">
         <v>7.0</v>
@@ -1359,7 +1359,7 @@
         <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>1175.0</v>
+        <v>1187.0</v>
       </c>
       <c r="G44" t="n">
         <v>1.0</v>
@@ -1671,7 +1671,7 @@
         <v>53</v>
       </c>
       <c r="F56" t="n">
-        <v>1760.0</v>
+        <v>1767.0</v>
       </c>
       <c r="G56" t="n">
         <v>4.0</v>
@@ -1697,7 +1697,7 @@
         <v>53</v>
       </c>
       <c r="F57" t="n">
-        <v>1635.0</v>
+        <v>1638.0</v>
       </c>
       <c r="G57" t="n">
         <v>2.0</v>
@@ -1775,7 +1775,7 @@
         <v>53</v>
       </c>
       <c r="F60" t="n">
-        <v>2829.0</v>
+        <v>2830.0</v>
       </c>
       <c r="G60" t="n">
         <v>8.0</v>
@@ -2165,7 +2165,7 @@
         <v>54</v>
       </c>
       <c r="F75" t="n">
-        <v>1120.0</v>
+        <v>1126.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2555,7 +2555,7 @@
         <v>54</v>
       </c>
       <c r="F90" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2607,7 +2607,7 @@
         <v>54</v>
       </c>
       <c r="F92" t="n">
-        <v>359.0</v>
+        <v>360.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2737,7 +2737,7 @@
         <v>54</v>
       </c>
       <c r="F97" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -3257,7 +3257,7 @@
         <v>54</v>
       </c>
       <c r="F117" t="n">
-        <v>12997.0</v>
+        <v>13029.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>619.0</v>
+        <v>620.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -3335,7 +3335,7 @@
         <v>54</v>
       </c>
       <c r="F120" t="n">
-        <v>1167.0</v>
+        <v>1170.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -397,7 +397,7 @@
         <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>1260.0</v>
+        <v>1261.0</v>
       </c>
       <c r="G7" t="n">
         <v>3.0</v>
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="F22" t="n">
-        <v>10977.0</v>
+        <v>11001.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>3552.0</v>
+        <v>3556.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -839,7 +839,7 @@
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>6796.0</v>
+        <v>6814.0</v>
       </c>
       <c r="G24" t="n">
         <v>47.0</v>
@@ -969,7 +969,7 @@
         <v>53</v>
       </c>
       <c r="F29" t="n">
-        <v>1690.0</v>
+        <v>1693.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1749,7 +1749,7 @@
         <v>53</v>
       </c>
       <c r="F59" t="n">
-        <v>1224.0</v>
+        <v>1225.0</v>
       </c>
       <c r="G59" t="n">
         <v>5.0</v>
@@ -2165,7 +2165,7 @@
         <v>54</v>
       </c>
       <c r="F75" t="n">
-        <v>1126.0</v>
+        <v>1129.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -3257,7 +3257,7 @@
         <v>54</v>
       </c>
       <c r="F117" t="n">
-        <v>13029.0</v>
+        <v>13047.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -1021,7 +1021,7 @@
         <v>53</v>
       </c>
       <c r="F31" t="n">
-        <v>2099.0</v>
+        <v>2100.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1359,7 +1359,7 @@
         <v>53</v>
       </c>
       <c r="F44" t="n">
-        <v>1187.0</v>
+        <v>1188.0</v>
       </c>
       <c r="G44" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -449,7 +449,7 @@
         <v>53</v>
       </c>
       <c r="F9" t="n">
-        <v>1449.0</v>
+        <v>1451.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -813,7 +813,7 @@
         <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>3556.0</v>
+        <v>3560.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -839,10 +839,10 @@
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>6814.0</v>
+        <v>6818.0</v>
       </c>
       <c r="G24" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="H24" t="n">
         <v>261.0</v>
@@ -891,7 +891,7 @@
         <v>53</v>
       </c>
       <c r="F26" t="n">
-        <v>6264.0</v>
+        <v>6272.0</v>
       </c>
       <c r="G26" t="n">
         <v>8.0</v>
@@ -943,7 +943,7 @@
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>4681.0</v>
+        <v>4684.0</v>
       </c>
       <c r="G28" t="n">
         <v>37.0</v>
@@ -1671,7 +1671,7 @@
         <v>53</v>
       </c>
       <c r="F56" t="n">
-        <v>1767.0</v>
+        <v>1774.0</v>
       </c>
       <c r="G56" t="n">
         <v>4.0</v>
@@ -1749,7 +1749,7 @@
         <v>53</v>
       </c>
       <c r="F59" t="n">
-        <v>1225.0</v>
+        <v>1226.0</v>
       </c>
       <c r="G59" t="n">
         <v>5.0</v>
@@ -1827,7 +1827,7 @@
         <v>53</v>
       </c>
       <c r="F62" t="n">
-        <v>1580.0</v>
+        <v>1581.0</v>
       </c>
       <c r="G62" t="n">
         <v>2.0</v>
@@ -2165,7 +2165,7 @@
         <v>54</v>
       </c>
       <c r="F75" t="n">
-        <v>1129.0</v>
+        <v>1131.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2607,7 +2607,7 @@
         <v>54</v>
       </c>
       <c r="F92" t="n">
-        <v>360.0</v>
+        <v>361.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -3257,7 +3257,7 @@
         <v>54</v>
       </c>
       <c r="F117" t="n">
-        <v>13047.0</v>
+        <v>13057.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>
@@ -3283,7 +3283,7 @@
         <v>54</v>
       </c>
       <c r="F118" t="n">
-        <v>620.0</v>
+        <v>623.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -3335,7 +3335,7 @@
         <v>54</v>
       </c>
       <c r="F120" t="n">
-        <v>1170.0</v>
+        <v>1171.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="57">
   <si>
     <t>Area</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Campania</t>
   </si>
   <si>
+    <t>Abruzzo</t>
+  </si>
+  <si>
     <t>Puglia</t>
   </si>
   <si>
@@ -165,6 +168,9 @@
   </si>
   <si>
     <t>Salerno</t>
+  </si>
+  <si>
+    <t>Chieti</t>
   </si>
   <si>
     <t>Bari</t>
@@ -261,10 +267,10 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
         <v>163.0</v>
@@ -287,10 +293,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
         <v>364.0</v>
@@ -313,10 +319,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
         <v>189.0</v>
@@ -339,13 +345,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>326.0</v>
+        <v>327.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -365,10 +371,10 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
         <v>762.0</v>
@@ -391,10 +397,10 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
         <v>1261.0</v>
@@ -417,13 +423,13 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>767.0</v>
+        <v>771.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -443,10 +449,10 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
         <v>1451.0</v>
@@ -469,10 +475,10 @@
         <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
         <v>1885.0</v>
@@ -495,13 +501,13 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>557.0</v>
+        <v>564.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -521,10 +527,10 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
         <v>8.0</v>
@@ -547,10 +553,10 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" t="n">
         <v>181.0</v>
@@ -573,10 +579,10 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F14" t="n">
         <v>227.0</v>
@@ -599,10 +605,10 @@
         <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F15" t="n">
         <v>478.0</v>
@@ -625,10 +631,10 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F16" t="n">
         <v>104.0</v>
@@ -651,10 +657,10 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F17" t="n">
         <v>486.0</v>
@@ -677,13 +683,13 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F18" t="n">
-        <v>3878.0</v>
+        <v>3889.0</v>
       </c>
       <c r="G18" t="n">
         <v>112.0</v>
@@ -703,13 +709,13 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F19" t="n">
-        <v>1752.0</v>
+        <v>1753.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -729,10 +735,10 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -741,7 +747,7 @@
         <v>0.0</v>
       </c>
       <c r="H20" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="21">
@@ -755,13 +761,13 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
-        <v>662.0</v>
+        <v>673.0</v>
       </c>
       <c r="G21" t="n">
         <v>22.0</v>
@@ -781,10 +787,10 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F22" t="n">
         <v>11001.0</v>
@@ -807,13 +813,13 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
-        <v>3560.0</v>
+        <v>3562.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -833,10 +839,10 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F24" t="n">
         <v>6818.0</v>
@@ -859,13 +865,13 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F25" t="n">
-        <v>3658.0</v>
+        <v>3660.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -885,10 +891,10 @@
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F26" t="n">
         <v>6272.0</v>
@@ -911,10 +917,10 @@
         <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F27" t="n">
         <v>1758.0</v>
@@ -937,10 +943,10 @@
         <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F28" t="n">
         <v>4684.0</v>
@@ -963,10 +969,10 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F29" t="n">
         <v>1693.0</v>
@@ -989,10 +995,10 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -1015,10 +1021,10 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F31" t="n">
         <v>2100.0</v>
@@ -1041,10 +1047,10 @@
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F32" t="n">
         <v>6.0</v>
@@ -1067,10 +1073,10 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F33" t="n">
         <v>123.0</v>
@@ -1093,10 +1099,10 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F34" t="n">
         <v>64.0</v>
@@ -1119,10 +1125,10 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F35" t="n">
         <v>15.0</v>
@@ -1145,10 +1151,10 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F36" t="n">
         <v>2.0</v>
@@ -1171,10 +1177,10 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F37" t="n">
         <v>16.0</v>
@@ -1197,10 +1203,10 @@
         <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F38" t="n">
         <v>2353.0</v>
@@ -1223,10 +1229,10 @@
         <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F39" t="n">
         <v>1737.0</v>
@@ -1249,10 +1255,10 @@
         <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F40" t="n">
         <v>627.0</v>
@@ -1275,10 +1281,10 @@
         <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F41" t="n">
         <v>101.0</v>
@@ -1301,10 +1307,10 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F42" t="n">
         <v>0.0</v>
@@ -1327,10 +1333,10 @@
         <v>17</v>
       </c>
       <c r="D43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F43" t="n">
         <v>1411.0</v>
@@ -1353,10 +1359,10 @@
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F44" t="n">
         <v>1188.0</v>
@@ -1379,13 +1385,13 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F45" t="n">
-        <v>649.0</v>
+        <v>652.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1405,10 +1411,10 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F46" t="n">
         <v>405.0</v>
@@ -1431,13 +1437,13 @@
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F47" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1457,10 +1463,10 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F48" t="n">
         <v>119.0</v>
@@ -1483,10 +1489,10 @@
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F49" t="n">
         <v>569.0</v>
@@ -1509,10 +1515,10 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F50" t="n">
         <v>1.0</v>
@@ -1535,13 +1541,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F51" t="n">
-        <v>145.0</v>
+        <v>148.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1561,10 +1567,10 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F52" t="n">
         <v>84.0</v>
@@ -1587,13 +1593,13 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F53" t="n">
-        <v>703.0</v>
+        <v>707.0</v>
       </c>
       <c r="G53" t="n">
         <v>3.0</v>
@@ -1613,10 +1619,10 @@
         <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F54" t="n">
         <v>1605.0</v>
@@ -1639,13 +1645,13 @@
         <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F55" t="n">
-        <v>758.0</v>
+        <v>761.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1665,10 +1671,10 @@
         <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F56" t="n">
         <v>1774.0</v>
@@ -1691,13 +1697,13 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E57" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F57" t="n">
-        <v>1638.0</v>
+        <v>1639.0</v>
       </c>
       <c r="G57" t="n">
         <v>2.0</v>
@@ -1717,10 +1723,10 @@
         <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E58" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F58" t="n">
         <v>1.0</v>
@@ -1743,13 +1749,13 @@
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E59" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F59" t="n">
-        <v>1226.0</v>
+        <v>1229.0</v>
       </c>
       <c r="G59" t="n">
         <v>5.0</v>
@@ -1769,10 +1775,10 @@
         <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F60" t="n">
         <v>2830.0</v>
@@ -1795,10 +1801,10 @@
         <v>16</v>
       </c>
       <c r="D61" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F61" t="n">
         <v>2.0</v>
@@ -1821,10 +1827,10 @@
         <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E62" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F62" t="n">
         <v>1581.0</v>
@@ -1847,10 +1853,10 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E63" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F63" t="n">
         <v>1.0</v>
@@ -1873,10 +1879,10 @@
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E64" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F64" t="n">
         <v>14.0</v>
@@ -1899,13 +1905,13 @@
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F65" t="n">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,13 +1931,13 @@
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E66" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F66" t="n">
-        <v>292.0</v>
+        <v>295.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,13 +1957,13 @@
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F67" t="n">
-        <v>2314.0</v>
+        <v>2335.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1977,13 +1983,13 @@
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F68" t="n">
-        <v>635.0</v>
+        <v>640.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2003,13 +2009,13 @@
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F69" t="n">
-        <v>161.0</v>
+        <v>165.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2029,10 +2035,10 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F70" t="n">
         <v>9.0</v>
@@ -2055,10 +2061,10 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F71" t="n">
         <v>1.0</v>
@@ -2081,13 +2087,13 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E72" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F72" t="n">
-        <v>2281.0</v>
+        <v>2289.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2107,10 +2113,10 @@
         <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E73" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F73" t="n">
         <v>848.0</v>
@@ -2133,10 +2139,10 @@
         <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F74" t="n">
         <v>131.0</v>
@@ -2159,13 +2165,13 @@
         <v>16</v>
       </c>
       <c r="D75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E75" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F75" t="n">
-        <v>1131.0</v>
+        <v>1141.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2185,10 +2191,10 @@
         <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E76" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F76" t="n">
         <v>13.0</v>
@@ -2211,10 +2217,10 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E77" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F77" t="n">
         <v>8.0</v>
@@ -2237,10 +2243,10 @@
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E78" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F78" t="n">
         <v>25.0</v>
@@ -2263,10 +2269,10 @@
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E79" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F79" t="n">
         <v>18.0</v>
@@ -2289,10 +2295,10 @@
         <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E80" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F80" t="n">
         <v>2.0</v>
@@ -2315,13 +2321,13 @@
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E81" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F81" t="n">
-        <v>96.0</v>
+        <v>100.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2341,13 +2347,13 @@
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F82" t="n">
-        <v>2929.0</v>
+        <v>2940.0</v>
       </c>
       <c r="G82" t="n">
         <v>2.0</v>
@@ -2367,13 +2373,13 @@
         <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E83" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F83" t="n">
-        <v>4511.0</v>
+        <v>4537.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2393,13 +2399,13 @@
         <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E84" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F84" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2419,10 +2425,10 @@
         <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E85" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F85" t="n">
         <v>32.0</v>
@@ -2445,10 +2451,10 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E86" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F86" t="n">
         <v>24.0</v>
@@ -2471,10 +2477,10 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E87" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F87" t="n">
         <v>30.0</v>
@@ -2497,10 +2503,10 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E88" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F88" t="n">
         <v>8.0</v>
@@ -2523,10 +2529,10 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E89" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F89" t="n">
         <v>74.0</v>
@@ -2549,10 +2555,10 @@
         <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F90" t="n">
         <v>138.0</v>
@@ -2575,10 +2581,10 @@
         <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E91" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F91" t="n">
         <v>1.0</v>
@@ -2601,13 +2607,13 @@
         <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E92" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F92" t="n">
-        <v>361.0</v>
+        <v>362.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2627,10 +2633,10 @@
         <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E93" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F93" t="n">
         <v>29.0</v>
@@ -2653,10 +2659,10 @@
         <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E94" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F94" t="n">
         <v>10.0</v>
@@ -2679,10 +2685,10 @@
         <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E95" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F95" t="n">
         <v>1.0</v>
@@ -2705,10 +2711,10 @@
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E96" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F96" t="n">
         <v>15.0</v>
@@ -2731,10 +2737,10 @@
         <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F97" t="n">
         <v>115.0</v>
@@ -2757,10 +2763,10 @@
         <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E98" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F98" t="n">
         <v>4.0</v>
@@ -2783,10 +2789,10 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E99" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F99" t="n">
         <v>7.0</v>
@@ -2809,10 +2815,10 @@
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E100" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F100" t="n">
         <v>0.0</v>
@@ -2835,10 +2841,10 @@
         <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E101" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F101" t="n">
         <v>9.0</v>
@@ -2861,10 +2867,10 @@
         <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E102" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F102" t="n">
         <v>40.0</v>
@@ -2884,16 +2890,16 @@
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E103" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F103" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2910,16 +2916,16 @@
         <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="E104" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F104" t="n">
-        <v>239.0</v>
+        <v>3.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2942,10 +2948,10 @@
         <v>22</v>
       </c>
       <c r="E105" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F105" t="n">
-        <v>529.0</v>
+        <v>242.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2968,10 +2974,10 @@
         <v>23</v>
       </c>
       <c r="E106" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F106" t="n">
-        <v>291.0</v>
+        <v>531.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -2994,10 +3000,10 @@
         <v>24</v>
       </c>
       <c r="E107" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F107" t="n">
-        <v>1.0</v>
+        <v>291.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3020,10 +3026,10 @@
         <v>25</v>
       </c>
       <c r="E108" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F108" t="n">
-        <v>297.0</v>
+        <v>1.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3040,16 +3046,16 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D109" t="s">
         <v>26</v>
       </c>
       <c r="E109" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F109" t="n">
-        <v>13.0</v>
+        <v>298.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3066,16 +3072,16 @@
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E110" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F110" t="n">
-        <v>4003.0</v>
+        <v>13.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3098,16 +3104,16 @@
         <v>43</v>
       </c>
       <c r="E111" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F111" t="n">
-        <v>7956.0</v>
+        <v>4006.0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112">
@@ -3124,16 +3130,16 @@
         <v>44</v>
       </c>
       <c r="E112" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F112" t="n">
-        <v>1228.0</v>
+        <v>7959.0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H112" t="n">
-        <v>670.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="113">
@@ -3147,19 +3153,19 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E113" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F113" t="n">
-        <v>3880.0</v>
+        <v>1228.0</v>
       </c>
       <c r="G113" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H113" t="n">
-        <v>23.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="114">
@@ -3173,19 +3179,19 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E114" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F114" t="n">
-        <v>76.0</v>
+        <v>3880.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="115">
@@ -3196,22 +3202,22 @@
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E115" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F115" t="n">
-        <v>334.0</v>
+        <v>77.0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H115" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -3228,16 +3234,16 @@
         <v>29</v>
       </c>
       <c r="E116" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F116" t="n">
-        <v>153.0</v>
+        <v>334.0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="117">
@@ -3254,13 +3260,13 @@
         <v>30</v>
       </c>
       <c r="E117" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F117" t="n">
-        <v>13057.0</v>
+        <v>153.0</v>
       </c>
       <c r="G117" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3277,19 +3283,19 @@
         <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E118" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F118" t="n">
-        <v>623.0</v>
+        <v>13072.0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="H118" t="n">
-        <v>105.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3306,16 +3312,16 @@
         <v>48</v>
       </c>
       <c r="E119" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F119" t="n">
-        <v>4.0</v>
+        <v>623.0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="120">
@@ -3332,16 +3338,16 @@
         <v>49</v>
       </c>
       <c r="E120" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F120" t="n">
-        <v>1171.0</v>
+        <v>4.0</v>
       </c>
       <c r="G120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H120" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -3352,22 +3358,22 @@
         <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E121" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F121" t="n">
+        <v>1171.0</v>
+      </c>
+      <c r="G121" t="n">
         <v>1.0</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H121" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="122">
@@ -3381,18 +3387,44 @@
         <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E122" t="s">
+        <v>56</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>8</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" t="s">
+        <v>21</v>
+      </c>
+      <c r="D123" t="s">
         <v>54</v>
       </c>
-      <c r="F122" t="n">
+      <c r="E123" t="s">
+        <v>56</v>
+      </c>
+      <c r="F123" t="n">
         <v>5.0</v>
       </c>
-      <c r="G122" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H122" t="n">
+      <c r="G123" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H123" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="60">
   <si>
     <t>Area</t>
   </si>
@@ -165,6 +165,15 @@
   </si>
   <si>
     <t>Vercelli</t>
+  </si>
+  <si>
+    <t>Arezzo</t>
+  </si>
+  <si>
+    <t>Livorno</t>
+  </si>
+  <si>
+    <t>Siena</t>
   </si>
   <si>
     <t>Salerno</t>
@@ -270,7 +279,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
         <v>163.0</v>
@@ -296,7 +305,7 @@
         <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
         <v>364.0</v>
@@ -322,7 +331,7 @@
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
         <v>189.0</v>
@@ -348,7 +357,7 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
         <v>327.0</v>
@@ -374,7 +383,7 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
         <v>762.0</v>
@@ -400,7 +409,7 @@
         <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
         <v>1261.0</v>
@@ -426,7 +435,7 @@
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" t="n">
         <v>771.0</v>
@@ -452,7 +461,7 @@
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
         <v>1451.0</v>
@@ -478,7 +487,7 @@
         <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" t="n">
         <v>1885.0</v>
@@ -504,10 +513,10 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>564.0</v>
+        <v>567.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -530,7 +539,7 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F12" t="n">
         <v>8.0</v>
@@ -556,10 +565,10 @@
         <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -582,7 +591,7 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
         <v>227.0</v>
@@ -608,10 +617,10 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>478.0</v>
+        <v>487.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -634,7 +643,7 @@
         <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F16" t="n">
         <v>104.0</v>
@@ -660,7 +669,7 @@
         <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F17" t="n">
         <v>486.0</v>
@@ -686,7 +695,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F18" t="n">
         <v>3889.0</v>
@@ -712,7 +721,7 @@
         <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F19" t="n">
         <v>1753.0</v>
@@ -721,7 +730,7 @@
         <v>55.0</v>
       </c>
       <c r="H19" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="20">
@@ -738,7 +747,7 @@
         <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -764,7 +773,7 @@
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
         <v>673.0</v>
@@ -790,7 +799,7 @@
         <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F22" t="n">
         <v>11001.0</v>
@@ -816,10 +825,10 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3562.0</v>
+        <v>3580.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -842,7 +851,7 @@
         <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F24" t="n">
         <v>6818.0</v>
@@ -868,7 +877,7 @@
         <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F25" t="n">
         <v>3660.0</v>
@@ -894,10 +903,10 @@
         <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>6272.0</v>
+        <v>6278.0</v>
       </c>
       <c r="G26" t="n">
         <v>8.0</v>
@@ -920,7 +929,7 @@
         <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
         <v>1758.0</v>
@@ -946,10 +955,10 @@
         <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>4684.0</v>
+        <v>4688.0</v>
       </c>
       <c r="G28" t="n">
         <v>37.0</v>
@@ -972,10 +981,10 @@
         <v>33</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1693.0</v>
+        <v>1697.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -998,7 +1007,7 @@
         <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -1024,10 +1033,10 @@
         <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2100.0</v>
+        <v>2103.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1050,7 +1059,7 @@
         <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F32" t="n">
         <v>6.0</v>
@@ -1076,7 +1085,7 @@
         <v>22</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F33" t="n">
         <v>123.0</v>
@@ -1102,7 +1111,7 @@
         <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F34" t="n">
         <v>64.0</v>
@@ -1128,7 +1137,7 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F35" t="n">
         <v>15.0</v>
@@ -1154,7 +1163,7 @@
         <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F36" t="n">
         <v>2.0</v>
@@ -1180,7 +1189,7 @@
         <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F37" t="n">
         <v>16.0</v>
@@ -1206,7 +1215,7 @@
         <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F38" t="n">
         <v>2353.0</v>
@@ -1232,7 +1241,7 @@
         <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F39" t="n">
         <v>1737.0</v>
@@ -1258,7 +1267,7 @@
         <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F40" t="n">
         <v>627.0</v>
@@ -1284,7 +1293,7 @@
         <v>33</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F41" t="n">
         <v>101.0</v>
@@ -1310,7 +1319,7 @@
         <v>40</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F42" t="n">
         <v>0.0</v>
@@ -1336,10 +1345,10 @@
         <v>41</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F43" t="n">
-        <v>1411.0</v>
+        <v>1416.0</v>
       </c>
       <c r="G43" t="n">
         <v>2.0</v>
@@ -1362,10 +1371,10 @@
         <v>35</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F44" t="n">
-        <v>1188.0</v>
+        <v>1194.0</v>
       </c>
       <c r="G44" t="n">
         <v>1.0</v>
@@ -1388,7 +1397,7 @@
         <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F45" t="n">
         <v>652.0</v>
@@ -1414,7 +1423,7 @@
         <v>23</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F46" t="n">
         <v>405.0</v>
@@ -1440,7 +1449,7 @@
         <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F47" t="n">
         <v>42.0</v>
@@ -1466,7 +1475,7 @@
         <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F48" t="n">
         <v>119.0</v>
@@ -1492,10 +1501,10 @@
         <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F49" t="n">
-        <v>569.0</v>
+        <v>570.0</v>
       </c>
       <c r="G49" t="n">
         <v>3.0</v>
@@ -1518,7 +1527,7 @@
         <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F50" t="n">
         <v>1.0</v>
@@ -1544,7 +1553,7 @@
         <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F51" t="n">
         <v>148.0</v>
@@ -1570,7 +1579,7 @@
         <v>44</v>
       </c>
       <c r="E52" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F52" t="n">
         <v>84.0</v>
@@ -1596,7 +1605,7 @@
         <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F53" t="n">
         <v>707.0</v>
@@ -1622,7 +1631,7 @@
         <v>28</v>
       </c>
       <c r="E54" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F54" t="n">
         <v>1605.0</v>
@@ -1648,7 +1657,7 @@
         <v>46</v>
       </c>
       <c r="E55" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F55" t="n">
         <v>761.0</v>
@@ -1674,10 +1683,10 @@
         <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>1774.0</v>
+        <v>1780.0</v>
       </c>
       <c r="G56" t="n">
         <v>4.0</v>
@@ -1700,10 +1709,10 @@
         <v>30</v>
       </c>
       <c r="E57" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F57" t="n">
-        <v>1639.0</v>
+        <v>1645.0</v>
       </c>
       <c r="G57" t="n">
         <v>2.0</v>
@@ -1726,7 +1735,7 @@
         <v>47</v>
       </c>
       <c r="E58" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F58" t="n">
         <v>1.0</v>
@@ -1752,10 +1761,10 @@
         <v>31</v>
       </c>
       <c r="E59" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F59" t="n">
-        <v>1229.0</v>
+        <v>1232.0</v>
       </c>
       <c r="G59" t="n">
         <v>5.0</v>
@@ -1778,10 +1787,10 @@
         <v>48</v>
       </c>
       <c r="E60" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>2830.0</v>
+        <v>2831.0</v>
       </c>
       <c r="G60" t="n">
         <v>8.0</v>
@@ -1804,7 +1813,7 @@
         <v>49</v>
       </c>
       <c r="E61" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F61" t="n">
         <v>2.0</v>
@@ -1830,7 +1839,7 @@
         <v>50</v>
       </c>
       <c r="E62" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F62" t="n">
         <v>1581.0</v>
@@ -1853,13 +1862,13 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E63" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F63" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1879,13 +1888,13 @@
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E64" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F64" t="n">
-        <v>14.0</v>
+        <v>521.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1899,19 +1908,19 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="E65" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F65" t="n">
-        <v>36.0</v>
+        <v>1.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1925,19 +1934,19 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E66" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F66" t="n">
-        <v>295.0</v>
+        <v>224.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1951,19 +1960,19 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E67" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F67" t="n">
-        <v>2335.0</v>
+        <v>14.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1977,19 +1986,19 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="E68" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F68" t="n">
-        <v>640.0</v>
+        <v>1.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2009,13 +2018,13 @@
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E69" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F69" t="n">
-        <v>165.0</v>
+        <v>36.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2032,16 +2041,16 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E70" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F70" t="n">
-        <v>9.0</v>
+        <v>295.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2058,16 +2067,16 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F71" t="n">
-        <v>1.0</v>
+        <v>2335.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2084,22 +2093,22 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F72" t="n">
-        <v>2289.0</v>
+        <v>640.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
       </c>
       <c r="H72" t="n">
-        <v>12778.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -2110,19 +2119,19 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E73" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F73" t="n">
-        <v>848.0</v>
+        <v>165.0</v>
       </c>
       <c r="G73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2136,16 +2145,16 @@
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F74" t="n">
-        <v>131.0</v>
+        <v>9.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -2162,19 +2171,19 @@
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E75" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1141.0</v>
+        <v>1.0</v>
       </c>
       <c r="G75" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2188,22 +2197,22 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F76" t="n">
-        <v>13.0</v>
+        <v>2289.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0</v>
+        <v>12778.0</v>
       </c>
     </row>
     <row r="77">
@@ -2214,19 +2223,19 @@
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D77" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F77" t="n">
-        <v>8.0</v>
+        <v>849.0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2240,16 +2249,16 @@
         <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D78" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E78" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F78" t="n">
-        <v>25.0</v>
+        <v>131.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2266,19 +2275,19 @@
         <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E79" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F79" t="n">
-        <v>18.0</v>
+        <v>1142.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2289,19 +2298,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E80" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F80" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2315,19 +2324,19 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E81" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F81" t="n">
-        <v>100.0</v>
+        <v>8.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2341,22 +2350,22 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E82" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F82" t="n">
-        <v>2940.0</v>
+        <v>25.0</v>
       </c>
       <c r="G82" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2367,25 +2376,25 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F83" t="n">
-        <v>4537.0</v>
+        <v>18.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
       </c>
       <c r="H83" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -2396,16 +2405,16 @@
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="E84" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F84" t="n">
-        <v>54.0</v>
+        <v>2.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2422,16 +2431,16 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F85" t="n">
-        <v>32.0</v>
+        <v>100.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2448,19 +2457,19 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F86" t="n">
-        <v>24.0</v>
+        <v>2940.0</v>
       </c>
       <c r="G86" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2474,22 +2483,22 @@
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F87" t="n">
-        <v>30.0</v>
+        <v>4537.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="88">
@@ -2500,16 +2509,16 @@
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F88" t="n">
-        <v>8.0</v>
+        <v>54.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2526,22 +2535,22 @@
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E89" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F89" t="n">
-        <v>74.0</v>
+        <v>32.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2552,19 +2561,19 @@
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E90" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F90" t="n">
-        <v>138.0</v>
+        <v>24.0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H90" t="n">
         <v>0.0</v>
@@ -2578,16 +2587,16 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E91" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F91" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2604,19 +2613,19 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E92" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>362.0</v>
+        <v>8.0</v>
       </c>
       <c r="G92" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H92" t="n">
         <v>0.0</v>
@@ -2630,22 +2639,22 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E93" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F93" t="n">
-        <v>29.0</v>
+        <v>74.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="94">
@@ -2656,16 +2665,16 @@
         <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F94" t="n">
-        <v>10.0</v>
+        <v>138.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2679,16 +2688,16 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E95" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F95" t="n">
         <v>1.0</v>
@@ -2705,22 +2714,22 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E96" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F96" t="n">
-        <v>15.0</v>
+        <v>363.0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2731,19 +2740,19 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E97" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F97" t="n">
-        <v>115.0</v>
+        <v>29.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2757,19 +2766,19 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E98" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F98" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -2786,16 +2795,16 @@
         <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D99" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E99" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F99" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2812,22 +2821,22 @@
         <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E100" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
       </c>
       <c r="H100" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="101">
@@ -2838,16 +2847,16 @@
         <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E101" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F101" t="n">
-        <v>9.0</v>
+        <v>115.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -2864,22 +2873,22 @@
         <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E102" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F102" t="n">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="G102" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H102" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="103">
@@ -2887,19 +2896,19 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D103" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E103" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F103" t="n">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2913,25 +2922,25 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D104" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E104" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F104" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="105">
@@ -2939,19 +2948,19 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D105" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E105" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F105" t="n">
-        <v>242.0</v>
+        <v>9.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2965,25 +2974,25 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D106" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E106" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F106" t="n">
-        <v>531.0</v>
+        <v>40.0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="107">
@@ -2994,16 +3003,16 @@
         <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D107" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="E107" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F107" t="n">
-        <v>291.0</v>
+        <v>11.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3020,16 +3029,16 @@
         <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E108" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F108" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3049,13 +3058,13 @@
         <v>13</v>
       </c>
       <c r="D109" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E109" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F109" t="n">
-        <v>298.0</v>
+        <v>242.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3072,16 +3081,16 @@
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D110" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E110" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F110" t="n">
-        <v>13.0</v>
+        <v>531.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3098,16 +3107,16 @@
         <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F111" t="n">
-        <v>4006.0</v>
+        <v>291.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -3124,22 +3133,22 @@
         <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D112" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E112" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F112" t="n">
-        <v>7959.0</v>
+        <v>1.0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H112" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="113">
@@ -3150,22 +3159,22 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D113" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E113" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F113" t="n">
-        <v>1228.0</v>
+        <v>298.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
       </c>
       <c r="H113" t="n">
-        <v>670.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="114">
@@ -3176,22 +3185,22 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E114" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F114" t="n">
-        <v>3880.0</v>
+        <v>13.0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H114" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="115">
@@ -3205,13 +3214,13 @@
         <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E115" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F115" t="n">
-        <v>77.0</v>
+        <v>4006.0</v>
       </c>
       <c r="G115" t="n">
         <v>0.0</v>
@@ -3228,22 +3237,22 @@
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D116" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E116" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>334.0</v>
+        <v>7959.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
       </c>
       <c r="H116" t="n">
-        <v>29.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="117">
@@ -3254,22 +3263,22 @@
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D117" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E117" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F117" t="n">
-        <v>153.0</v>
+        <v>1228.0</v>
       </c>
       <c r="G117" t="n">
         <v>0.0</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="118">
@@ -3280,22 +3289,22 @@
         <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D118" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E118" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F118" t="n">
-        <v>13072.0</v>
+        <v>3880.0</v>
       </c>
       <c r="G118" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="119">
@@ -3306,22 +3315,22 @@
         <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D119" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E119" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F119" t="n">
-        <v>623.0</v>
+        <v>77.0</v>
       </c>
       <c r="G119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H119" t="n">
-        <v>105.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -3335,19 +3344,19 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E120" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F120" t="n">
-        <v>4.0</v>
+        <v>336.0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H120" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="121">
@@ -3361,19 +3370,19 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E121" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F121" t="n">
-        <v>1171.0</v>
+        <v>153.0</v>
       </c>
       <c r="G121" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H121" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="122">
@@ -3384,19 +3393,19 @@
         <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="E122" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F122" t="n">
-        <v>1.0</v>
+        <v>13086.0</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3410,21 +3419,203 @@
         <v>12</v>
       </c>
       <c r="C123" t="s">
+        <v>16</v>
+      </c>
+      <c r="D123" t="s">
+        <v>48</v>
+      </c>
+      <c r="E123" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" t="n">
+        <v>626.0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>105.0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>8</v>
+      </c>
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C124" t="s">
+        <v>16</v>
+      </c>
+      <c r="D124" t="s">
+        <v>49</v>
+      </c>
+      <c r="E124" t="s">
+        <v>59</v>
+      </c>
+      <c r="F124" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" t="s">
+        <v>16</v>
+      </c>
+      <c r="D125" t="s">
+        <v>50</v>
+      </c>
+      <c r="E125" t="s">
+        <v>59</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1171.0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" t="s">
+        <v>20</v>
+      </c>
+      <c r="D126" t="s">
+        <v>56</v>
+      </c>
+      <c r="E126" t="s">
+        <v>59</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>8</v>
+      </c>
+      <c r="B127" t="s">
+        <v>12</v>
+      </c>
+      <c r="C127" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127" t="s">
+        <v>32</v>
+      </c>
+      <c r="E127" t="s">
+        <v>59</v>
+      </c>
+      <c r="F127" t="n">
+        <v>136.0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>8</v>
+      </c>
+      <c r="B128" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" t="s">
+        <v>52</v>
+      </c>
+      <c r="E128" t="s">
+        <v>59</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>8</v>
+      </c>
+      <c r="B129" t="s">
+        <v>12</v>
+      </c>
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" t="s">
+        <v>34</v>
+      </c>
+      <c r="E129" t="s">
+        <v>59</v>
+      </c>
+      <c r="F129" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>8</v>
+      </c>
+      <c r="B130" t="s">
+        <v>12</v>
+      </c>
+      <c r="C130" t="s">
         <v>21</v>
       </c>
-      <c r="D123" t="s">
-        <v>54</v>
-      </c>
-      <c r="E123" t="s">
-        <v>56</v>
-      </c>
-      <c r="F123" t="n">
+      <c r="D130" t="s">
+        <v>57</v>
+      </c>
+      <c r="E130" t="s">
+        <v>59</v>
+      </c>
+      <c r="F130" t="n">
         <v>5.0</v>
       </c>
-      <c r="G123" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H123" t="n">
+      <c r="G130" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H130" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -386,7 +386,7 @@
         <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>762.0</v>
+        <v>765.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -412,7 +412,7 @@
         <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>1261.0</v>
+        <v>1262.0</v>
       </c>
       <c r="G7" t="n">
         <v>3.0</v>
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1451.0</v>
+        <v>1457.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1885.0</v>
+        <v>1886.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>567.0</v>
+        <v>573.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -568,7 +568,7 @@
         <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>487.0</v>
+        <v>489.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -698,7 +698,7 @@
         <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>3889.0</v>
+        <v>3891.0</v>
       </c>
       <c r="G18" t="n">
         <v>112.0</v>
@@ -724,7 +724,7 @@
         <v>58</v>
       </c>
       <c r="F19" t="n">
-        <v>1753.0</v>
+        <v>1754.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11001.0</v>
+        <v>11014.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3580.0</v>
+        <v>3586.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -854,7 +854,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6818.0</v>
+        <v>6831.0</v>
       </c>
       <c r="G24" t="n">
         <v>49.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>6278.0</v>
+        <v>6279.0</v>
       </c>
       <c r="G26" t="n">
         <v>8.0</v>
@@ -964,7 +964,7 @@
         <v>37.0</v>
       </c>
       <c r="H28" t="n">
-        <v>15.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="29">
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1697.0</v>
+        <v>1698.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1374,7 +1374,7 @@
         <v>58</v>
       </c>
       <c r="F44" t="n">
-        <v>1194.0</v>
+        <v>1203.0</v>
       </c>
       <c r="G44" t="n">
         <v>1.0</v>
@@ -1400,7 +1400,7 @@
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>652.0</v>
+        <v>653.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1478,7 +1478,7 @@
         <v>58</v>
       </c>
       <c r="F48" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>1780.0</v>
+        <v>1784.0</v>
       </c>
       <c r="G56" t="n">
         <v>4.0</v>
@@ -1712,7 +1712,7 @@
         <v>58</v>
       </c>
       <c r="F57" t="n">
-        <v>1645.0</v>
+        <v>1646.0</v>
       </c>
       <c r="G57" t="n">
         <v>2.0</v>
@@ -1764,7 +1764,7 @@
         <v>58</v>
       </c>
       <c r="F59" t="n">
-        <v>1232.0</v>
+        <v>1234.0</v>
       </c>
       <c r="G59" t="n">
         <v>5.0</v>
@@ -1842,7 +1842,7 @@
         <v>58</v>
       </c>
       <c r="F62" t="n">
-        <v>1581.0</v>
+        <v>1582.0</v>
       </c>
       <c r="G62" t="n">
         <v>2.0</v>
@@ -1894,7 +1894,7 @@
         <v>58</v>
       </c>
       <c r="F64" t="n">
-        <v>521.0</v>
+        <v>525.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1946,7 +1946,7 @@
         <v>58</v>
       </c>
       <c r="F66" t="n">
-        <v>224.0</v>
+        <v>234.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1972,7 +1972,7 @@
         <v>58</v>
       </c>
       <c r="F67" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2050,7 +2050,7 @@
         <v>59</v>
       </c>
       <c r="F70" t="n">
-        <v>295.0</v>
+        <v>303.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2076,7 +2076,7 @@
         <v>59</v>
       </c>
       <c r="F71" t="n">
-        <v>2335.0</v>
+        <v>2347.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2102,7 +2102,7 @@
         <v>59</v>
       </c>
       <c r="F72" t="n">
-        <v>640.0</v>
+        <v>642.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2128,7 +2128,7 @@
         <v>59</v>
       </c>
       <c r="F73" t="n">
-        <v>165.0</v>
+        <v>174.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2284,7 +2284,7 @@
         <v>59</v>
       </c>
       <c r="F79" t="n">
-        <v>1142.0</v>
+        <v>1144.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2466,7 +2466,7 @@
         <v>59</v>
       </c>
       <c r="F86" t="n">
-        <v>2940.0</v>
+        <v>2964.0</v>
       </c>
       <c r="G86" t="n">
         <v>2.0</v>
@@ -2492,7 +2492,7 @@
         <v>59</v>
       </c>
       <c r="F87" t="n">
-        <v>4537.0</v>
+        <v>4556.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2518,7 +2518,7 @@
         <v>59</v>
       </c>
       <c r="F88" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2674,7 +2674,7 @@
         <v>59</v>
       </c>
       <c r="F94" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2726,7 +2726,7 @@
         <v>59</v>
       </c>
       <c r="F96" t="n">
-        <v>363.0</v>
+        <v>364.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -3116,7 +3116,7 @@
         <v>59</v>
       </c>
       <c r="F111" t="n">
-        <v>291.0</v>
+        <v>292.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -3168,7 +3168,7 @@
         <v>59</v>
       </c>
       <c r="F113" t="n">
-        <v>298.0</v>
+        <v>300.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -3350,7 +3350,7 @@
         <v>59</v>
       </c>
       <c r="F120" t="n">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -3402,7 +3402,7 @@
         <v>59</v>
       </c>
       <c r="F122" t="n">
-        <v>13086.0</v>
+        <v>13088.0</v>
       </c>
       <c r="G122" t="n">
         <v>13.0</v>
@@ -3428,7 +3428,7 @@
         <v>59</v>
       </c>
       <c r="F123" t="n">
-        <v>626.0</v>
+        <v>627.0</v>
       </c>
       <c r="G123" t="n">
         <v>1.0</v>
@@ -3480,7 +3480,7 @@
         <v>59</v>
       </c>
       <c r="F125" t="n">
-        <v>1171.0</v>
+        <v>1172.0</v>
       </c>
       <c r="G125" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1457.0</v>
+        <v>1463.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1886.0</v>
+        <v>1896.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>573.0</v>
+        <v>577.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -568,7 +568,7 @@
         <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>183.0</v>
+        <v>185.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3586.0</v>
+        <v>3587.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -854,7 +854,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6831.0</v>
+        <v>6833.0</v>
       </c>
       <c r="G24" t="n">
         <v>49.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>6279.0</v>
+        <v>6287.0</v>
       </c>
       <c r="G26" t="n">
         <v>8.0</v>
@@ -961,7 +961,7 @@
         <v>4688.0</v>
       </c>
       <c r="G28" t="n">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
       <c r="H28" t="n">
         <v>18.0</v>
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1698.0</v>
+        <v>1700.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1270,7 +1270,7 @@
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>627.0</v>
+        <v>628.0</v>
       </c>
       <c r="G40" t="n">
         <v>4.0</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>1784.0</v>
+        <v>1787.0</v>
       </c>
       <c r="G56" t="n">
         <v>4.0</v>
@@ -1712,7 +1712,7 @@
         <v>58</v>
       </c>
       <c r="F57" t="n">
-        <v>1646.0</v>
+        <v>1648.0</v>
       </c>
       <c r="G57" t="n">
         <v>2.0</v>
@@ -1894,7 +1894,7 @@
         <v>58</v>
       </c>
       <c r="F64" t="n">
-        <v>525.0</v>
+        <v>527.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -2284,7 +2284,7 @@
         <v>59</v>
       </c>
       <c r="F79" t="n">
-        <v>1144.0</v>
+        <v>1151.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2726,7 +2726,7 @@
         <v>59</v>
       </c>
       <c r="F96" t="n">
-        <v>364.0</v>
+        <v>365.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -3350,7 +3350,7 @@
         <v>59</v>
       </c>
       <c r="F120" t="n">
-        <v>337.0</v>
+        <v>338.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -3402,7 +3402,7 @@
         <v>59</v>
       </c>
       <c r="F122" t="n">
-        <v>13088.0</v>
+        <v>13114.0</v>
       </c>
       <c r="G122" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -1374,7 +1374,7 @@
         <v>58</v>
       </c>
       <c r="F44" t="n">
-        <v>1203.0</v>
+        <v>1208.0</v>
       </c>
       <c r="G44" t="n">
         <v>1.0</v>
@@ -1894,7 +1894,7 @@
         <v>58</v>
       </c>
       <c r="F64" t="n">
-        <v>527.0</v>
+        <v>528.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1972,7 +1972,7 @@
         <v>58</v>
       </c>
       <c r="F67" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -308,7 +308,7 @@
         <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>364.0</v>
+        <v>368.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -334,7 +334,7 @@
         <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -386,7 +386,7 @@
         <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>765.0</v>
+        <v>773.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -412,7 +412,7 @@
         <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>1262.0</v>
+        <v>1263.0</v>
       </c>
       <c r="G7" t="n">
         <v>3.0</v>
@@ -672,7 +672,7 @@
         <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>486.0</v>
+        <v>487.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
@@ -698,7 +698,7 @@
         <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>3891.0</v>
+        <v>3902.0</v>
       </c>
       <c r="G18" t="n">
         <v>112.0</v>
@@ -776,7 +776,7 @@
         <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>673.0</v>
+        <v>677.0</v>
       </c>
       <c r="G21" t="n">
         <v>22.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3587.0</v>
+        <v>3594.0</v>
       </c>
       <c r="G23" t="n">
         <v>20.0</v>
@@ -854,7 +854,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6833.0</v>
+        <v>6842.0</v>
       </c>
       <c r="G24" t="n">
         <v>49.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>6287.0</v>
+        <v>6289.0</v>
       </c>
       <c r="G26" t="n">
         <v>8.0</v>
@@ -932,7 +932,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>1758.0</v>
+        <v>1759.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>4688.0</v>
+        <v>4691.0</v>
       </c>
       <c r="G28" t="n">
         <v>40.0</v>
@@ -1114,7 +1114,7 @@
         <v>58</v>
       </c>
       <c r="F34" t="n">
-        <v>64.0</v>
+        <v>66.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1426,7 +1426,7 @@
         <v>58</v>
       </c>
       <c r="F46" t="n">
-        <v>405.0</v>
+        <v>419.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1478,7 +1478,7 @@
         <v>58</v>
       </c>
       <c r="F48" t="n">
-        <v>120.0</v>
+        <v>123.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1504,7 +1504,7 @@
         <v>58</v>
       </c>
       <c r="F49" t="n">
-        <v>570.0</v>
+        <v>571.0</v>
       </c>
       <c r="G49" t="n">
         <v>3.0</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>1787.0</v>
+        <v>1789.0</v>
       </c>
       <c r="G56" t="n">
         <v>4.0</v>
@@ -1764,10 +1764,10 @@
         <v>58</v>
       </c>
       <c r="F59" t="n">
-        <v>1234.0</v>
+        <v>1236.0</v>
       </c>
       <c r="G59" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>2831.0</v>
+        <v>2835.0</v>
       </c>
       <c r="G60" t="n">
         <v>8.0</v>
@@ -2050,7 +2050,7 @@
         <v>59</v>
       </c>
       <c r="F70" t="n">
-        <v>303.0</v>
+        <v>305.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2076,7 +2076,7 @@
         <v>59</v>
       </c>
       <c r="F71" t="n">
-        <v>2347.0</v>
+        <v>2352.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2102,7 +2102,7 @@
         <v>59</v>
       </c>
       <c r="F72" t="n">
-        <v>642.0</v>
+        <v>643.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2128,7 +2128,7 @@
         <v>59</v>
       </c>
       <c r="F73" t="n">
-        <v>174.0</v>
+        <v>178.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2284,7 +2284,7 @@
         <v>59</v>
       </c>
       <c r="F79" t="n">
-        <v>1151.0</v>
+        <v>1156.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2466,7 +2466,7 @@
         <v>59</v>
       </c>
       <c r="F86" t="n">
-        <v>2964.0</v>
+        <v>2968.0</v>
       </c>
       <c r="G86" t="n">
         <v>2.0</v>
@@ -2492,7 +2492,7 @@
         <v>59</v>
       </c>
       <c r="F87" t="n">
-        <v>4556.0</v>
+        <v>4560.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2518,7 +2518,7 @@
         <v>59</v>
       </c>
       <c r="F88" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2726,7 +2726,7 @@
         <v>59</v>
       </c>
       <c r="F96" t="n">
-        <v>365.0</v>
+        <v>366.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -3350,7 +3350,7 @@
         <v>59</v>
       </c>
       <c r="F120" t="n">
-        <v>338.0</v>
+        <v>339.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -3402,7 +3402,7 @@
         <v>59</v>
       </c>
       <c r="F122" t="n">
-        <v>13114.0</v>
+        <v>13130.0</v>
       </c>
       <c r="G122" t="n">
         <v>13.0</v>
@@ -3428,7 +3428,7 @@
         <v>59</v>
       </c>
       <c r="F123" t="n">
-        <v>627.0</v>
+        <v>628.0</v>
       </c>
       <c r="G123" t="n">
         <v>1.0</v>
@@ -3480,7 +3480,7 @@
         <v>59</v>
       </c>
       <c r="F125" t="n">
-        <v>1172.0</v>
+        <v>1174.0</v>
       </c>
       <c r="G125" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -438,7 +438,7 @@
         <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>771.0</v>
+        <v>772.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1463.0</v>
+        <v>1464.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>577.0</v>
+        <v>578.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11014.0</v>
+        <v>11023.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -831,7 +831,7 @@
         <v>3594.0</v>
       </c>
       <c r="G23" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="H23" t="n">
         <v>76.0</v>
@@ -880,7 +880,7 @@
         <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>3660.0</v>
+        <v>3662.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>6289.0</v>
+        <v>6292.0</v>
       </c>
       <c r="G26" t="n">
         <v>8.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>4691.0</v>
+        <v>4693.0</v>
       </c>
       <c r="G28" t="n">
         <v>40.0</v>
@@ -1218,7 +1218,7 @@
         <v>58</v>
       </c>
       <c r="F38" t="n">
-        <v>2353.0</v>
+        <v>2354.0</v>
       </c>
       <c r="G38" t="n">
         <v>13.0</v>
@@ -1556,7 +1556,7 @@
         <v>58</v>
       </c>
       <c r="F51" t="n">
-        <v>148.0</v>
+        <v>152.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G52" t="n">
         <v>1.0</v>
@@ -1634,7 +1634,7 @@
         <v>58</v>
       </c>
       <c r="F54" t="n">
-        <v>1605.0</v>
+        <v>1613.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>761.0</v>
+        <v>765.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>1789.0</v>
+        <v>1791.0</v>
       </c>
       <c r="G56" t="n">
         <v>4.0</v>
@@ -1712,7 +1712,7 @@
         <v>58</v>
       </c>
       <c r="F57" t="n">
-        <v>1648.0</v>
+        <v>1651.0</v>
       </c>
       <c r="G57" t="n">
         <v>2.0</v>
@@ -1894,7 +1894,7 @@
         <v>58</v>
       </c>
       <c r="F64" t="n">
-        <v>528.0</v>
+        <v>530.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -2206,7 +2206,7 @@
         <v>59</v>
       </c>
       <c r="F76" t="n">
-        <v>2289.0</v>
+        <v>2293.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2232,7 +2232,7 @@
         <v>59</v>
       </c>
       <c r="F77" t="n">
-        <v>849.0</v>
+        <v>850.0</v>
       </c>
       <c r="G77" t="n">
         <v>1.0</v>
@@ -2284,7 +2284,7 @@
         <v>59</v>
       </c>
       <c r="F79" t="n">
-        <v>1156.0</v>
+        <v>1160.0</v>
       </c>
       <c r="G79" t="n">
         <v>1.0</v>
@@ -2726,7 +2726,7 @@
         <v>59</v>
       </c>
       <c r="F96" t="n">
-        <v>366.0</v>
+        <v>367.0</v>
       </c>
       <c r="G96" t="n">
         <v>1.0</v>
@@ -3220,7 +3220,7 @@
         <v>59</v>
       </c>
       <c r="F115" t="n">
-        <v>4006.0</v>
+        <v>4009.0</v>
       </c>
       <c r="G115" t="n">
         <v>0.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>7959.0</v>
+        <v>7961.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3402,7 +3402,7 @@
         <v>59</v>
       </c>
       <c r="F122" t="n">
-        <v>13130.0</v>
+        <v>13146.0</v>
       </c>
       <c r="G122" t="n">
         <v>13.0</v>
@@ -3428,7 +3428,7 @@
         <v>59</v>
       </c>
       <c r="F123" t="n">
-        <v>628.0</v>
+        <v>630.0</v>
       </c>
       <c r="G123" t="n">
         <v>1.0</v>
@@ -3480,7 +3480,7 @@
         <v>59</v>
       </c>
       <c r="F125" t="n">
-        <v>1174.0</v>
+        <v>1176.0</v>
       </c>
       <c r="G125" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="60">
   <si>
     <t>Area</t>
   </si>
@@ -282,7 +282,7 @@
         <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>163.0</v>
+        <v>171.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1464.0</v>
+        <v>1467.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1896.0</v>
+        <v>1899.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>578.0</v>
+        <v>591.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -542,7 +542,7 @@
         <v>58</v>
       </c>
       <c r="F12" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -568,7 +568,7 @@
         <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>489.0</v>
+        <v>490.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -672,7 +672,7 @@
         <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>487.0</v>
+        <v>488.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3594.0</v>
+        <v>3602.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,13 +854,13 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6842.0</v>
+        <v>6862.0</v>
       </c>
       <c r="G24" t="n">
         <v>49.0</v>
       </c>
       <c r="H24" t="n">
-        <v>261.0</v>
+        <v>273.0</v>
       </c>
     </row>
     <row r="25">
@@ -906,13 +906,13 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>6292.0</v>
+        <v>8667.0</v>
       </c>
       <c r="G26" t="n">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="H26" t="n">
-        <v>572.0</v>
+        <v>715.0</v>
       </c>
     </row>
     <row r="27">
@@ -932,13 +932,13 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>1759.0</v>
+        <v>3505.0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H27" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="28">
@@ -958,10 +958,10 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>4693.0</v>
+        <v>5326.0</v>
       </c>
       <c r="G28" t="n">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="H28" t="n">
         <v>18.0</v>
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1700.0</v>
+        <v>1706.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2103.0</v>
+        <v>2112.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1183,22 +1183,22 @@
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E37" t="s">
         <v>58</v>
       </c>
       <c r="F37" t="n">
-        <v>16.0</v>
+        <v>101.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
       </c>
       <c r="H37" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -1209,22 +1209,22 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
       </c>
       <c r="F38" t="n">
-        <v>2354.0</v>
+        <v>0.0</v>
       </c>
       <c r="G38" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H38" t="n">
-        <v>143.0</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="39">
@@ -1235,22 +1235,22 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
         <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>1737.0</v>
+        <v>1422.0</v>
       </c>
       <c r="G39" t="n">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="H39" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -1261,22 +1261,22 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E40" t="s">
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>628.0</v>
+        <v>1214.0</v>
       </c>
       <c r="G40" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="41">
@@ -1284,19 +1284,19 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E41" t="s">
         <v>58</v>
       </c>
       <c r="F41" t="n">
-        <v>101.0</v>
+        <v>672.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1310,25 +1310,25 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E42" t="s">
         <v>58</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0</v>
+        <v>419.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
       </c>
       <c r="H42" t="n">
-        <v>163.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -1336,22 +1336,22 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
         <v>58</v>
       </c>
       <c r="F43" t="n">
-        <v>1416.0</v>
+        <v>42.0</v>
       </c>
       <c r="G43" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1362,25 +1362,25 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E44" t="s">
         <v>58</v>
       </c>
       <c r="F44" t="n">
-        <v>1208.0</v>
+        <v>123.0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H44" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -1391,19 +1391,19 @@
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>653.0</v>
+        <v>571.0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1417,16 +1417,16 @@
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
         <v>58</v>
       </c>
       <c r="F46" t="n">
-        <v>419.0</v>
+        <v>1.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1443,16 +1443,16 @@
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
         <v>58</v>
       </c>
       <c r="F47" t="n">
-        <v>42.0</v>
+        <v>152.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1469,19 +1469,19 @@
         <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
         <v>58</v>
       </c>
       <c r="F48" t="n">
-        <v>123.0</v>
+        <v>86.0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1495,22 +1495,22 @@
         <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
         <v>58</v>
       </c>
       <c r="F49" t="n">
-        <v>571.0</v>
+        <v>707.0</v>
       </c>
       <c r="G49" t="n">
         <v>3.0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="50">
@@ -1524,19 +1524,19 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E50" t="s">
         <v>58</v>
       </c>
       <c r="F50" t="n">
-        <v>1.0</v>
+        <v>1613.0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="51">
@@ -1550,13 +1550,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E51" t="s">
         <v>58</v>
       </c>
       <c r="F51" t="n">
-        <v>152.0</v>
+        <v>765.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1573,22 +1573,22 @@
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>86.0</v>
+        <v>1793.0</v>
       </c>
       <c r="G52" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H52" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -1599,22 +1599,22 @@
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>707.0</v>
+        <v>1663.0</v>
       </c>
       <c r="G53" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H53" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -1625,22 +1625,22 @@
         <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E54" t="s">
         <v>58</v>
       </c>
       <c r="F54" t="n">
-        <v>1613.0</v>
+        <v>1.0</v>
       </c>
       <c r="G54" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H54" t="n">
-        <v>86.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -1651,19 +1651,19 @@
         <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>765.0</v>
+        <v>1239.0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1680,19 +1680,19 @@
         <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E56" t="s">
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>1791.0</v>
+        <v>2835.0</v>
       </c>
       <c r="G56" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="57">
@@ -1706,16 +1706,16 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E57" t="s">
         <v>58</v>
       </c>
       <c r="F57" t="n">
-        <v>1651.0</v>
+        <v>2.0</v>
       </c>
       <c r="G57" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H57" t="n">
         <v>0.0</v>
@@ -1732,16 +1732,16 @@
         <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E58" t="s">
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1.0</v>
+        <v>1582.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1755,19 +1755,19 @@
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E59" t="s">
         <v>58</v>
       </c>
       <c r="F59" t="n">
-        <v>1236.0</v>
+        <v>2.0</v>
       </c>
       <c r="G59" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1781,22 +1781,22 @@
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E60" t="s">
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>2835.0</v>
+        <v>531.0</v>
       </c>
       <c r="G60" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H60" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -1807,16 +1807,16 @@
         <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E61" t="s">
         <v>58</v>
       </c>
       <c r="F61" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1833,19 +1833,19 @@
         <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E62" t="s">
         <v>58</v>
       </c>
       <c r="F62" t="n">
-        <v>1582.0</v>
+        <v>234.0</v>
       </c>
       <c r="G62" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1862,13 +1862,13 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E63" t="s">
         <v>58</v>
       </c>
       <c r="F63" t="n">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1888,13 +1888,13 @@
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E64" t="s">
         <v>58</v>
       </c>
       <c r="F64" t="n">
-        <v>530.0</v>
+        <v>1.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1908,19 +1908,19 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F65" t="n">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1934,19 +1934,19 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F66" t="n">
-        <v>234.0</v>
+        <v>314.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1960,19 +1960,19 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F67" t="n">
-        <v>16.0</v>
+        <v>2358.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1986,19 +1986,19 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F68" t="n">
-        <v>1.0</v>
+        <v>647.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2018,13 +2018,13 @@
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
         <v>59</v>
       </c>
       <c r="F69" t="n">
-        <v>36.0</v>
+        <v>181.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2041,16 +2041,16 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E70" t="s">
         <v>59</v>
       </c>
       <c r="F70" t="n">
-        <v>305.0</v>
+        <v>9.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2067,16 +2067,16 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
         <v>59</v>
       </c>
       <c r="F71" t="n">
-        <v>2352.0</v>
+        <v>1.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2093,22 +2093,22 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E72" t="s">
         <v>59</v>
       </c>
       <c r="F72" t="n">
-        <v>643.0</v>
+        <v>2293.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0</v>
+        <v>12778.0</v>
       </c>
     </row>
     <row r="73">
@@ -2119,19 +2119,19 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E73" t="s">
         <v>59</v>
       </c>
       <c r="F73" t="n">
-        <v>178.0</v>
+        <v>850.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2145,16 +2145,16 @@
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E74" t="s">
         <v>59</v>
       </c>
       <c r="F74" t="n">
-        <v>9.0</v>
+        <v>132.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -2171,19 +2171,19 @@
         <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D75" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E75" t="s">
         <v>59</v>
       </c>
       <c r="F75" t="n">
+        <v>1160.0</v>
+      </c>
+      <c r="G75" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2197,22 +2197,22 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D76" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E76" t="s">
         <v>59</v>
       </c>
       <c r="F76" t="n">
-        <v>2293.0</v>
+        <v>13.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>12778.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -2223,19 +2223,19 @@
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E77" t="s">
         <v>59</v>
       </c>
       <c r="F77" t="n">
-        <v>850.0</v>
+        <v>8.0</v>
       </c>
       <c r="G77" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2249,16 +2249,16 @@
         <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E78" t="s">
         <v>59</v>
       </c>
       <c r="F78" t="n">
-        <v>131.0</v>
+        <v>25.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2275,19 +2275,19 @@
         <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E79" t="s">
         <v>59</v>
       </c>
       <c r="F79" t="n">
-        <v>1160.0</v>
+        <v>18.0</v>
       </c>
       <c r="G79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H79" t="n">
         <v>0.0</v>
@@ -2298,19 +2298,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E80" t="s">
         <v>59</v>
       </c>
       <c r="F80" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2324,19 +2324,19 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E81" t="s">
         <v>59</v>
       </c>
       <c r="F81" t="n">
-        <v>8.0</v>
+        <v>105.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2350,22 +2350,22 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E82" t="s">
         <v>59</v>
       </c>
       <c r="F82" t="n">
-        <v>25.0</v>
+        <v>2971.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2376,25 +2376,25 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E83" t="s">
         <v>59</v>
       </c>
       <c r="F83" t="n">
-        <v>18.0</v>
+        <v>4579.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="84">
@@ -2405,16 +2405,16 @@
         <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="E84" t="s">
         <v>59</v>
       </c>
       <c r="F84" t="n">
-        <v>2.0</v>
+        <v>56.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2431,16 +2431,16 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E85" t="s">
         <v>59</v>
       </c>
       <c r="F85" t="n">
-        <v>100.0</v>
+        <v>32.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2457,19 +2457,19 @@
         <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E86" t="s">
         <v>59</v>
       </c>
       <c r="F86" t="n">
-        <v>2968.0</v>
+        <v>24.0</v>
       </c>
       <c r="G86" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2483,22 +2483,22 @@
         <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E87" t="s">
         <v>59</v>
       </c>
       <c r="F87" t="n">
-        <v>4560.0</v>
+        <v>30.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -2509,16 +2509,16 @@
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E88" t="s">
         <v>59</v>
       </c>
       <c r="F88" t="n">
-        <v>56.0</v>
+        <v>8.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2535,22 +2535,22 @@
         <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E89" t="s">
         <v>59</v>
       </c>
       <c r="F89" t="n">
-        <v>32.0</v>
+        <v>74.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="90">
@@ -2561,19 +2561,19 @@
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
         <v>59</v>
       </c>
       <c r="F90" t="n">
-        <v>24.0</v>
+        <v>254.0</v>
       </c>
       <c r="G90" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H90" t="n">
         <v>0.0</v>
@@ -2587,16 +2587,16 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E91" t="s">
         <v>59</v>
       </c>
       <c r="F91" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2613,19 +2613,19 @@
         <v>10</v>
       </c>
       <c r="C92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E92" t="s">
         <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>8.0</v>
+        <v>367.0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H92" t="n">
         <v>0.0</v>
@@ -2639,22 +2639,22 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E93" t="s">
         <v>59</v>
       </c>
       <c r="F93" t="n">
-        <v>74.0</v>
+        <v>29.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="94">
@@ -2665,16 +2665,16 @@
         <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="E94" t="s">
         <v>59</v>
       </c>
       <c r="F94" t="n">
-        <v>139.0</v>
+        <v>10.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2688,13 +2688,13 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E95" t="s">
         <v>59</v>
@@ -2714,22 +2714,22 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E96" t="s">
         <v>59</v>
       </c>
       <c r="F96" t="n">
-        <v>367.0</v>
+        <v>15.0</v>
       </c>
       <c r="G96" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2740,7 +2740,7 @@
         <v>8</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C97" t="s">
         <v>17</v>
@@ -2752,7 +2752,7 @@
         <v>59</v>
       </c>
       <c r="F97" t="n">
-        <v>29.0</v>
+        <v>7.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2766,25 +2766,25 @@
         <v>8</v>
       </c>
       <c r="B98" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C98" t="s">
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E98" t="s">
         <v>59</v>
       </c>
       <c r="F98" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="99">
@@ -2795,16 +2795,16 @@
         <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E99" t="s">
         <v>59</v>
       </c>
       <c r="F99" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2821,22 +2821,22 @@
         <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E100" t="s">
         <v>59</v>
       </c>
       <c r="F100" t="n">
-        <v>15.0</v>
+        <v>40.0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="101">
@@ -2844,19 +2844,19 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D101" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="E101" t="s">
         <v>59</v>
       </c>
       <c r="F101" t="n">
-        <v>115.0</v>
+        <v>11.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -2870,19 +2870,19 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D102" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="E102" t="s">
         <v>59</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G102" t="n">
         <v>0.0</v>
@@ -2896,19 +2896,19 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E103" t="s">
         <v>59</v>
       </c>
       <c r="F103" t="n">
-        <v>7.0</v>
+        <v>242.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2922,25 +2922,25 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E104" t="s">
         <v>59</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0</v>
+        <v>531.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
       </c>
       <c r="H104" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="105">
@@ -2948,19 +2948,19 @@
         <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E105" t="s">
         <v>59</v>
       </c>
       <c r="F105" t="n">
-        <v>9.0</v>
+        <v>293.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2974,25 +2974,25 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
       </c>
       <c r="F106" t="n">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H106" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -3003,16 +3003,16 @@
         <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="E107" t="s">
         <v>59</v>
       </c>
       <c r="F107" t="n">
-        <v>11.0</v>
+        <v>300.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3029,16 +3029,16 @@
         <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="E108" t="s">
         <v>59</v>
       </c>
       <c r="F108" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3055,16 +3055,16 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E109" t="s">
         <v>59</v>
       </c>
       <c r="F109" t="n">
-        <v>242.0</v>
+        <v>4009.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3081,22 +3081,22 @@
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D110" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E110" t="s">
         <v>59</v>
       </c>
       <c r="F110" t="n">
-        <v>531.0</v>
+        <v>7961.0</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H110" t="n">
-        <v>0.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="111">
@@ -3107,22 +3107,22 @@
         <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="E111" t="s">
         <v>59</v>
       </c>
       <c r="F111" t="n">
-        <v>292.0</v>
+        <v>1228.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
       </c>
       <c r="H111" t="n">
-        <v>0.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="112">
@@ -3133,22 +3133,22 @@
         <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E112" t="s">
         <v>59</v>
       </c>
       <c r="F112" t="n">
+        <v>3880.0</v>
+      </c>
+      <c r="G112" t="n">
         <v>1.0</v>
       </c>
-      <c r="G112" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H112" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="113">
@@ -3159,16 +3159,16 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E113" t="s">
         <v>59</v>
       </c>
       <c r="F113" t="n">
-        <v>300.0</v>
+        <v>77.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -3185,22 +3185,22 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D114" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E114" t="s">
         <v>59</v>
       </c>
       <c r="F114" t="n">
-        <v>13.0</v>
+        <v>339.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="115">
@@ -3211,16 +3211,16 @@
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E115" t="s">
         <v>59</v>
       </c>
       <c r="F115" t="n">
-        <v>4009.0</v>
+        <v>153.0</v>
       </c>
       <c r="G115" t="n">
         <v>0.0</v>
@@ -3237,22 +3237,22 @@
         <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E116" t="s">
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>7961.0</v>
+        <v>13147.0</v>
       </c>
       <c r="G116" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="H116" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="117">
@@ -3263,22 +3263,22 @@
         <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E117" t="s">
         <v>59</v>
       </c>
       <c r="F117" t="n">
-        <v>1228.0</v>
+        <v>630.0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H117" t="n">
-        <v>670.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="118">
@@ -3289,22 +3289,22 @@
         <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E118" t="s">
         <v>59</v>
       </c>
       <c r="F118" t="n">
-        <v>3880.0</v>
+        <v>4.0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H118" t="n">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3315,22 +3315,22 @@
         <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E119" t="s">
         <v>59</v>
       </c>
       <c r="F119" t="n">
-        <v>77.0</v>
+        <v>1178.0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="120">
@@ -3341,22 +3341,22 @@
         <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="E120" t="s">
         <v>59</v>
       </c>
       <c r="F120" t="n">
-        <v>339.0</v>
+        <v>1.0</v>
       </c>
       <c r="G120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H120" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -3367,16 +3367,16 @@
         <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E121" t="s">
         <v>59</v>
       </c>
       <c r="F121" t="n">
-        <v>153.0</v>
+        <v>136.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>
@@ -3393,19 +3393,19 @@
         <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E122" t="s">
         <v>59</v>
       </c>
       <c r="F122" t="n">
-        <v>13146.0</v>
+        <v>1.0</v>
       </c>
       <c r="G122" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H122" t="n">
         <v>0.0</v>
@@ -3419,22 +3419,22 @@
         <v>12</v>
       </c>
       <c r="C123" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E123" t="s">
         <v>59</v>
       </c>
       <c r="F123" t="n">
-        <v>630.0</v>
+        <v>50.0</v>
       </c>
       <c r="G123" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H123" t="n">
-        <v>105.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -3445,177 +3445,21 @@
         <v>12</v>
       </c>
       <c r="C124" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D124" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E124" t="s">
         <v>59</v>
       </c>
       <c r="F124" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G124" t="n">
         <v>0.0</v>
       </c>
       <c r="H124" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>8</v>
-      </c>
-      <c r="B125" t="s">
-        <v>12</v>
-      </c>
-      <c r="C125" t="s">
-        <v>16</v>
-      </c>
-      <c r="D125" t="s">
-        <v>50</v>
-      </c>
-      <c r="E125" t="s">
-        <v>59</v>
-      </c>
-      <c r="F125" t="n">
-        <v>1176.0</v>
-      </c>
-      <c r="G125" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>8</v>
-      </c>
-      <c r="B126" t="s">
-        <v>12</v>
-      </c>
-      <c r="C126" t="s">
-        <v>20</v>
-      </c>
-      <c r="D126" t="s">
-        <v>56</v>
-      </c>
-      <c r="E126" t="s">
-        <v>59</v>
-      </c>
-      <c r="F126" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>8</v>
-      </c>
-      <c r="B127" t="s">
-        <v>12</v>
-      </c>
-      <c r="C127" t="s">
-        <v>17</v>
-      </c>
-      <c r="D127" t="s">
-        <v>32</v>
-      </c>
-      <c r="E127" t="s">
-        <v>59</v>
-      </c>
-      <c r="F127" t="n">
-        <v>136.0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>8</v>
-      </c>
-      <c r="B128" t="s">
-        <v>12</v>
-      </c>
-      <c r="C128" t="s">
-        <v>17</v>
-      </c>
-      <c r="D128" t="s">
-        <v>52</v>
-      </c>
-      <c r="E128" t="s">
-        <v>59</v>
-      </c>
-      <c r="F128" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>8</v>
-      </c>
-      <c r="B129" t="s">
-        <v>12</v>
-      </c>
-      <c r="C129" t="s">
-        <v>17</v>
-      </c>
-      <c r="D129" t="s">
-        <v>34</v>
-      </c>
-      <c r="E129" t="s">
-        <v>59</v>
-      </c>
-      <c r="F129" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>8</v>
-      </c>
-      <c r="B130" t="s">
-        <v>12</v>
-      </c>
-      <c r="C130" t="s">
-        <v>21</v>
-      </c>
-      <c r="D130" t="s">
-        <v>57</v>
-      </c>
-      <c r="E130" t="s">
-        <v>59</v>
-      </c>
-      <c r="F130" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H130" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>591.0</v>
+        <v>594.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>490.0</v>
+        <v>493.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11023.0</v>
+        <v>11025.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3602.0</v>
+        <v>3604.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -860,7 +860,7 @@
         <v>49.0</v>
       </c>
       <c r="H24" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
     </row>
     <row r="25">
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8667.0</v>
+        <v>8671.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -932,7 +932,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>3505.0</v>
+        <v>3506.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -1244,7 +1244,7 @@
         <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>1422.0</v>
+        <v>1423.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1270,7 +1270,7 @@
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>1214.0</v>
+        <v>1224.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1400,7 +1400,7 @@
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>571.0</v>
+        <v>579.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>1793.0</v>
+        <v>1794.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1663.0</v>
+        <v>1672.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1239.0</v>
+        <v>1260.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>531.0</v>
+        <v>535.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -2128,7 +2128,7 @@
         <v>59</v>
       </c>
       <c r="F73" t="n">
-        <v>850.0</v>
+        <v>851.0</v>
       </c>
       <c r="G73" t="n">
         <v>1.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1160.0</v>
+        <v>1164.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2622,7 +2622,7 @@
         <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>367.0</v>
+        <v>369.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13147.0</v>
+        <v>13185.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>
@@ -3272,7 +3272,7 @@
         <v>59</v>
       </c>
       <c r="F117" t="n">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>594.0</v>
+        <v>596.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11025.0</v>
+        <v>11028.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3604.0</v>
+        <v>3606.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,13 +854,13 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6862.0</v>
+        <v>6863.0</v>
       </c>
       <c r="G24" t="n">
         <v>49.0</v>
       </c>
       <c r="H24" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
     </row>
     <row r="25">
@@ -958,13 +958,13 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5326.0</v>
+        <v>5329.0</v>
       </c>
       <c r="G28" t="n">
         <v>44.0</v>
       </c>
       <c r="H28" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="29">
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1706.0</v>
+        <v>1712.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2112.0</v>
+        <v>2114.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1270,7 +1270,7 @@
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>1224.0</v>
+        <v>1225.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1400,7 +1400,7 @@
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>579.0</v>
+        <v>581.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1260.0</v>
+        <v>1262.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>535.0</v>
+        <v>548.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1842,7 +1842,7 @@
         <v>58</v>
       </c>
       <c r="F62" t="n">
-        <v>234.0</v>
+        <v>241.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1164.0</v>
+        <v>1168.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2856,7 +2856,7 @@
         <v>59</v>
       </c>
       <c r="F101" t="n">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13185.0</v>
+        <v>13195.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -568,7 +568,7 @@
         <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1712.0</v>
+        <v>1714.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2114.0</v>
+        <v>2117.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>548.0</v>
+        <v>549.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1842,7 +1842,7 @@
         <v>58</v>
       </c>
       <c r="F62" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1868,7 +1868,7 @@
         <v>58</v>
       </c>
       <c r="F63" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -412,10 +412,10 @@
         <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>1263.0</v>
+        <v>1264.0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H7" t="n">
         <v>0.0</v>
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1467.0</v>
+        <v>1472.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1899.0</v>
+        <v>1901.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>596.0</v>
+        <v>611.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -802,13 +802,13 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11028.0</v>
+        <v>11039.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
       </c>
       <c r="H22" t="n">
-        <v>1023.0</v>
+        <v>1024.0</v>
       </c>
     </row>
     <row r="23">
@@ -854,10 +854,10 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6863.0</v>
+        <v>6868.0</v>
       </c>
       <c r="G24" t="n">
-        <v>49.0</v>
+        <v>46.0</v>
       </c>
       <c r="H24" t="n">
         <v>275.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8671.0</v>
+        <v>8685.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -932,7 +932,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>3506.0</v>
+        <v>3510.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5329.0</v>
+        <v>5332.0</v>
       </c>
       <c r="G28" t="n">
         <v>44.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>1794.0</v>
+        <v>1800.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1672.0</v>
+        <v>1677.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1262.0</v>
+        <v>1270.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1738,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1582.0</v>
+        <v>1583.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -2154,7 +2154,7 @@
         <v>59</v>
       </c>
       <c r="F74" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1168.0</v>
+        <v>1174.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13195.0</v>
+        <v>13212.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>
@@ -3272,7 +3272,7 @@
         <v>59</v>
       </c>
       <c r="F117" t="n">
-        <v>631.0</v>
+        <v>632.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -438,7 +438,7 @@
         <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>772.0</v>
+        <v>774.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1901.0</v>
+        <v>1902.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>611.0</v>
+        <v>618.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3606.0</v>
+        <v>3610.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,7 +854,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6868.0</v>
+        <v>6887.0</v>
       </c>
       <c r="G24" t="n">
         <v>46.0</v>
@@ -880,7 +880,7 @@
         <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>3662.0</v>
+        <v>3668.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5332.0</v>
+        <v>5346.0</v>
       </c>
       <c r="G28" t="n">
         <v>44.0</v>
@@ -1400,7 +1400,7 @@
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>581.0</v>
+        <v>600.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1452,7 +1452,7 @@
         <v>58</v>
       </c>
       <c r="F47" t="n">
-        <v>152.0</v>
+        <v>158.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1530,7 +1530,7 @@
         <v>58</v>
       </c>
       <c r="F50" t="n">
-        <v>1613.0</v>
+        <v>1617.0</v>
       </c>
       <c r="G50" t="n">
         <v>4.0</v>
@@ -1556,7 +1556,7 @@
         <v>58</v>
       </c>
       <c r="F51" t="n">
-        <v>765.0</v>
+        <v>768.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1677.0</v>
+        <v>1681.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1270.0</v>
+        <v>1290.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>549.0</v>
+        <v>552.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1946,7 +1946,7 @@
         <v>59</v>
       </c>
       <c r="F66" t="n">
-        <v>314.0</v>
+        <v>321.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1972,7 +1972,7 @@
         <v>59</v>
       </c>
       <c r="F67" t="n">
-        <v>2358.0</v>
+        <v>2371.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1998,7 +1998,7 @@
         <v>59</v>
       </c>
       <c r="F68" t="n">
-        <v>647.0</v>
+        <v>649.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2024,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="F69" t="n">
-        <v>181.0</v>
+        <v>183.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2102,7 +2102,7 @@
         <v>59</v>
       </c>
       <c r="F72" t="n">
-        <v>2293.0</v>
+        <v>2307.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1174.0</v>
+        <v>1181.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2362,7 +2362,7 @@
         <v>59</v>
       </c>
       <c r="F82" t="n">
-        <v>2971.0</v>
+        <v>2991.0</v>
       </c>
       <c r="G82" t="n">
         <v>2.0</v>
@@ -2388,7 +2388,7 @@
         <v>59</v>
       </c>
       <c r="F83" t="n">
-        <v>4579.0</v>
+        <v>4595.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2518,7 +2518,7 @@
         <v>59</v>
       </c>
       <c r="F88" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2934,7 +2934,7 @@
         <v>59</v>
       </c>
       <c r="F104" t="n">
-        <v>531.0</v>
+        <v>534.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -3012,7 +3012,7 @@
         <v>59</v>
       </c>
       <c r="F107" t="n">
-        <v>300.0</v>
+        <v>303.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3090,7 +3090,7 @@
         <v>59</v>
       </c>
       <c r="F110" t="n">
-        <v>7961.0</v>
+        <v>7962.0</v>
       </c>
       <c r="G110" t="n">
         <v>1.0</v>
@@ -3200,7 +3200,7 @@
         <v>1.0</v>
       </c>
       <c r="H114" t="n">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="115">
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13212.0</v>
+        <v>13221.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>
@@ -3278,7 +3278,7 @@
         <v>1.0</v>
       </c>
       <c r="H117" t="n">
-        <v>105.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="118">
@@ -3330,7 +3330,7 @@
         <v>1.0</v>
       </c>
       <c r="H119" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="120">

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -568,7 +568,7 @@
         <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>493.0</v>
+        <v>496.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3610.0</v>
+        <v>3627.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1714.0</v>
+        <v>1727.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1016,7 +1016,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="31">
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2117.0</v>
+        <v>2128.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1244,7 +1244,7 @@
         <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>1423.0</v>
+        <v>1442.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1270,13 +1270,13 @@
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>1225.0</v>
+        <v>1228.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
       </c>
       <c r="H40" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="41">
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>552.0</v>
+        <v>554.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1842,7 +1842,7 @@
         <v>58</v>
       </c>
       <c r="F62" t="n">
-        <v>242.0</v>
+        <v>245.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -415,7 +415,7 @@
         <v>1264.0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H7" t="n">
         <v>0.0</v>
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1472.0</v>
+        <v>1476.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1902.0</v>
+        <v>1906.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>618.0</v>
+        <v>625.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -594,7 +594,7 @@
         <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>227.0</v>
+        <v>229.0</v>
       </c>
       <c r="G14" t="n">
         <v>2.0</v>
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>496.0</v>
+        <v>508.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11039.0</v>
+        <v>11040.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3627.0</v>
+        <v>3634.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,10 +854,10 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6887.0</v>
+        <v>6894.0</v>
       </c>
       <c r="G24" t="n">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
       <c r="H24" t="n">
         <v>275.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8685.0</v>
+        <v>8706.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -932,7 +932,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>3510.0</v>
+        <v>3528.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5346.0</v>
+        <v>5350.0</v>
       </c>
       <c r="G28" t="n">
         <v>44.0</v>
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1727.0</v>
+        <v>1730.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2128.0</v>
+        <v>2134.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1244,7 +1244,7 @@
         <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>1442.0</v>
+        <v>1444.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1400,7 +1400,7 @@
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>600.0</v>
+        <v>629.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>1800.0</v>
+        <v>1804.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1681.0</v>
+        <v>1702.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1290.0</v>
+        <v>1293.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1738,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1583.0</v>
+        <v>1584.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>554.0</v>
+        <v>564.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1842,7 +1842,7 @@
         <v>58</v>
       </c>
       <c r="F62" t="n">
-        <v>245.0</v>
+        <v>249.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2128,7 +2128,7 @@
         <v>59</v>
       </c>
       <c r="F73" t="n">
-        <v>851.0</v>
+        <v>852.0</v>
       </c>
       <c r="G73" t="n">
         <v>1.0</v>
@@ -2154,7 +2154,7 @@
         <v>59</v>
       </c>
       <c r="F74" t="n">
-        <v>133.0</v>
+        <v>136.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1181.0</v>
+        <v>1186.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2570,7 +2570,7 @@
         <v>59</v>
       </c>
       <c r="F90" t="n">
-        <v>254.0</v>
+        <v>256.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2622,7 +2622,7 @@
         <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>369.0</v>
+        <v>371.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13221.0</v>
+        <v>13260.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>
@@ -3272,7 +3272,7 @@
         <v>59</v>
       </c>
       <c r="F117" t="n">
-        <v>632.0</v>
+        <v>633.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -3324,7 +3324,7 @@
         <v>59</v>
       </c>
       <c r="F119" t="n">
-        <v>1178.0</v>
+        <v>1179.0</v>
       </c>
       <c r="G119" t="n">
         <v>1.0</v>
@@ -3376,7 +3376,7 @@
         <v>59</v>
       </c>
       <c r="F121" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>625.0</v>
+        <v>627.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -568,7 +568,7 @@
         <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3634.0</v>
+        <v>3635.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,7 +854,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6894.0</v>
+        <v>6912.0</v>
       </c>
       <c r="G24" t="n">
         <v>49.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5350.0</v>
+        <v>5356.0</v>
       </c>
       <c r="G28" t="n">
         <v>44.0</v>
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1730.0</v>
+        <v>1731.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1293.0</v>
+        <v>1314.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>2835.0</v>
+        <v>2837.0</v>
       </c>
       <c r="G56" t="n">
         <v>8.0</v>
@@ -1738,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1584.0</v>
+        <v>1586.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>564.0</v>
+        <v>565.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1186.0</v>
+        <v>1187.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13260.0</v>
+        <v>13274.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>
@@ -3272,7 +3272,7 @@
         <v>59</v>
       </c>
       <c r="F117" t="n">
-        <v>633.0</v>
+        <v>637.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>
@@ -3324,7 +3324,7 @@
         <v>59</v>
       </c>
       <c r="F119" t="n">
-        <v>1179.0</v>
+        <v>1180.0</v>
       </c>
       <c r="G119" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>508.0</v>
+        <v>509.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2134.0</v>
+        <v>2137.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1244,7 +1244,7 @@
         <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>1444.0</v>
+        <v>1447.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1270,7 +1270,7 @@
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>1228.0</v>
+        <v>1234.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>565.0</v>
+        <v>566.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1868,7 +1868,7 @@
         <v>58</v>
       </c>
       <c r="F63" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -3376,7 +3376,7 @@
         <v>59</v>
       </c>
       <c r="F121" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -282,7 +282,7 @@
         <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -308,7 +308,7 @@
         <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>368.0</v>
+        <v>374.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -360,7 +360,7 @@
         <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>327.0</v>
+        <v>328.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -386,7 +386,7 @@
         <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>773.0</v>
+        <v>777.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1476.0</v>
+        <v>1480.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1906.0</v>
+        <v>1908.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>627.0</v>
+        <v>639.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -672,7 +672,7 @@
         <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>488.0</v>
+        <v>501.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
@@ -698,10 +698,10 @@
         <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>3902.0</v>
+        <v>3909.0</v>
       </c>
       <c r="G18" t="n">
-        <v>112.0</v>
+        <v>116.0</v>
       </c>
       <c r="H18" t="n">
         <v>422.0</v>
@@ -724,7 +724,7 @@
         <v>58</v>
       </c>
       <c r="F19" t="n">
-        <v>1754.0</v>
+        <v>1764.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -776,7 +776,7 @@
         <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>677.0</v>
+        <v>682.0</v>
       </c>
       <c r="G21" t="n">
         <v>22.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11040.0</v>
+        <v>11064.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3635.0</v>
+        <v>3639.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8706.0</v>
+        <v>8714.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -932,7 +932,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>3528.0</v>
+        <v>3530.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -958,10 +958,10 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5356.0</v>
+        <v>5366.0</v>
       </c>
       <c r="G28" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="H28" t="n">
         <v>19.0</v>
@@ -1088,7 +1088,7 @@
         <v>58</v>
       </c>
       <c r="F33" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1114,7 +1114,7 @@
         <v>58</v>
       </c>
       <c r="F34" t="n">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1296,7 +1296,7 @@
         <v>58</v>
       </c>
       <c r="F41" t="n">
-        <v>672.0</v>
+        <v>680.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1322,7 +1322,7 @@
         <v>58</v>
       </c>
       <c r="F42" t="n">
-        <v>419.0</v>
+        <v>430.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1374,7 +1374,7 @@
         <v>58</v>
       </c>
       <c r="F44" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>1804.0</v>
+        <v>1809.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1702.0</v>
+        <v>1706.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1314.0</v>
+        <v>1325.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1738,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1586.0</v>
+        <v>1587.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -1920,7 +1920,7 @@
         <v>59</v>
       </c>
       <c r="F65" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1946,7 +1946,7 @@
         <v>59</v>
       </c>
       <c r="F66" t="n">
-        <v>321.0</v>
+        <v>331.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1972,7 +1972,7 @@
         <v>59</v>
       </c>
       <c r="F67" t="n">
-        <v>2371.0</v>
+        <v>2387.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1998,7 +1998,7 @@
         <v>59</v>
       </c>
       <c r="F68" t="n">
-        <v>649.0</v>
+        <v>653.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2024,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="F69" t="n">
-        <v>183.0</v>
+        <v>187.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1187.0</v>
+        <v>1191.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2362,7 +2362,7 @@
         <v>59</v>
       </c>
       <c r="F82" t="n">
-        <v>2991.0</v>
+        <v>3005.0</v>
       </c>
       <c r="G82" t="n">
         <v>2.0</v>
@@ -2388,7 +2388,7 @@
         <v>59</v>
       </c>
       <c r="F83" t="n">
-        <v>4595.0</v>
+        <v>4623.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2414,7 +2414,7 @@
         <v>59</v>
       </c>
       <c r="F84" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2622,7 +2622,7 @@
         <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>371.0</v>
+        <v>373.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2726,7 +2726,7 @@
         <v>59</v>
       </c>
       <c r="F96" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2908,7 +2908,7 @@
         <v>59</v>
       </c>
       <c r="F103" t="n">
-        <v>242.0</v>
+        <v>244.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2934,7 +2934,7 @@
         <v>59</v>
       </c>
       <c r="F104" t="n">
-        <v>534.0</v>
+        <v>540.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -3012,7 +3012,7 @@
         <v>59</v>
       </c>
       <c r="F107" t="n">
-        <v>303.0</v>
+        <v>305.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3194,7 +3194,7 @@
         <v>59</v>
       </c>
       <c r="F114" t="n">
-        <v>339.0</v>
+        <v>340.0</v>
       </c>
       <c r="G114" t="n">
         <v>1.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13274.0</v>
+        <v>13283.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1908.0</v>
+        <v>1910.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -730,7 +730,7 @@
         <v>55.0</v>
       </c>
       <c r="H19" t="n">
-        <v>234.0</v>
+        <v>236.0</v>
       </c>
     </row>
     <row r="20">
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3639.0</v>
+        <v>3643.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,10 +854,10 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6912.0</v>
+        <v>6916.0</v>
       </c>
       <c r="G24" t="n">
-        <v>49.0</v>
+        <v>45.0</v>
       </c>
       <c r="H24" t="n">
         <v>275.0</v>
@@ -880,7 +880,7 @@
         <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>3668.0</v>
+        <v>3672.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8714.0</v>
+        <v>8724.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -932,7 +932,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>3530.0</v>
+        <v>3531.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5366.0</v>
+        <v>5367.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -1452,7 +1452,7 @@
         <v>58</v>
       </c>
       <c r="F47" t="n">
-        <v>158.0</v>
+        <v>166.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1504,7 +1504,7 @@
         <v>58</v>
       </c>
       <c r="F49" t="n">
-        <v>707.0</v>
+        <v>709.0</v>
       </c>
       <c r="G49" t="n">
         <v>3.0</v>
@@ -1530,7 +1530,7 @@
         <v>58</v>
       </c>
       <c r="F50" t="n">
-        <v>1617.0</v>
+        <v>1623.0</v>
       </c>
       <c r="G50" t="n">
         <v>4.0</v>
@@ -1556,7 +1556,7 @@
         <v>58</v>
       </c>
       <c r="F51" t="n">
-        <v>768.0</v>
+        <v>771.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>2837.0</v>
+        <v>2838.0</v>
       </c>
       <c r="G56" t="n">
         <v>8.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>566.0</v>
+        <v>570.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -2102,7 +2102,7 @@
         <v>59</v>
       </c>
       <c r="F72" t="n">
-        <v>2307.0</v>
+        <v>2319.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1191.0</v>
+        <v>1197.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2570,7 +2570,7 @@
         <v>59</v>
       </c>
       <c r="F90" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2830,7 +2830,7 @@
         <v>59</v>
       </c>
       <c r="F100" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>
@@ -3064,7 +3064,7 @@
         <v>59</v>
       </c>
       <c r="F109" t="n">
-        <v>4009.0</v>
+        <v>4011.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3090,7 +3090,7 @@
         <v>59</v>
       </c>
       <c r="F110" t="n">
-        <v>7962.0</v>
+        <v>7963.0</v>
       </c>
       <c r="G110" t="n">
         <v>1.0</v>
@@ -3116,7 +3116,7 @@
         <v>59</v>
       </c>
       <c r="F111" t="n">
-        <v>1228.0</v>
+        <v>1229.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -3168,7 +3168,7 @@
         <v>59</v>
       </c>
       <c r="F113" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13283.0</v>
+        <v>13301.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>639.0</v>
+        <v>655.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -568,7 +568,7 @@
         <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>189.0</v>
+        <v>192.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>509.0</v>
+        <v>515.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -678,7 +678,7 @@
         <v>15.0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="18">
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11064.0</v>
+        <v>11102.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3643.0</v>
+        <v>3677.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,7 +854,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6916.0</v>
+        <v>6919.0</v>
       </c>
       <c r="G24" t="n">
         <v>45.0</v>
@@ -906,13 +906,13 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8724.0</v>
+        <v>8733.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
       </c>
       <c r="H26" t="n">
-        <v>715.0</v>
+        <v>716.0</v>
       </c>
     </row>
     <row r="27">
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5367.0</v>
+        <v>5384.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1731.0</v>
+        <v>1739.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2137.0</v>
+        <v>2150.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1244,7 +1244,7 @@
         <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>1447.0</v>
+        <v>1477.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1270,13 +1270,13 @@
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>1234.0</v>
+        <v>1236.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
       </c>
       <c r="H40" t="n">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="41">
@@ -1400,7 +1400,7 @@
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>629.0</v>
+        <v>642.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>1809.0</v>
+        <v>1822.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1325.0</v>
+        <v>1334.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1738,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1587.0</v>
+        <v>1588.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>570.0</v>
+        <v>574.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1868,7 +1868,7 @@
         <v>58</v>
       </c>
       <c r="F63" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -2128,7 +2128,7 @@
         <v>59</v>
       </c>
       <c r="F73" t="n">
-        <v>852.0</v>
+        <v>853.0</v>
       </c>
       <c r="G73" t="n">
         <v>1.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1197.0</v>
+        <v>1201.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2258,7 +2258,7 @@
         <v>59</v>
       </c>
       <c r="F78" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2570,7 +2570,7 @@
         <v>59</v>
       </c>
       <c r="F90" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2622,7 +2622,7 @@
         <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>373.0</v>
+        <v>375.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13301.0</v>
+        <v>13323.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -282,7 +282,7 @@
         <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -308,7 +308,7 @@
         <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>374.0</v>
+        <v>377.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -334,7 +334,7 @@
         <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>190.0</v>
+        <v>192.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -360,7 +360,7 @@
         <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -386,7 +386,7 @@
         <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>777.0</v>
+        <v>787.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1480.0</v>
+        <v>1482.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1910.0</v>
+        <v>1927.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>655.0</v>
+        <v>656.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -594,7 +594,7 @@
         <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>229.0</v>
+        <v>230.0</v>
       </c>
       <c r="G14" t="n">
         <v>2.0</v>
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>515.0</v>
+        <v>517.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -672,7 +672,7 @@
         <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>501.0</v>
+        <v>507.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
@@ -698,7 +698,7 @@
         <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>3909.0</v>
+        <v>3913.0</v>
       </c>
       <c r="G18" t="n">
         <v>116.0</v>
@@ -724,7 +724,7 @@
         <v>58</v>
       </c>
       <c r="F19" t="n">
-        <v>1764.0</v>
+        <v>1772.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -776,7 +776,7 @@
         <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>682.0</v>
+        <v>701.0</v>
       </c>
       <c r="G21" t="n">
         <v>22.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11102.0</v>
+        <v>11116.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8733.0</v>
+        <v>8743.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -932,7 +932,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>3531.0</v>
+        <v>3559.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5384.0</v>
+        <v>5385.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -1088,7 +1088,7 @@
         <v>58</v>
       </c>
       <c r="F33" t="n">
-        <v>124.0</v>
+        <v>128.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1114,7 +1114,7 @@
         <v>58</v>
       </c>
       <c r="F34" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1166,7 +1166,7 @@
         <v>58</v>
       </c>
       <c r="F36" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1270,7 +1270,7 @@
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>1236.0</v>
+        <v>1238.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1296,7 +1296,7 @@
         <v>58</v>
       </c>
       <c r="F41" t="n">
-        <v>680.0</v>
+        <v>682.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1322,7 +1322,7 @@
         <v>58</v>
       </c>
       <c r="F42" t="n">
-        <v>430.0</v>
+        <v>443.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1374,7 +1374,7 @@
         <v>58</v>
       </c>
       <c r="F44" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1706.0</v>
+        <v>1744.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1334.0</v>
+        <v>1367.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1738,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1588.0</v>
+        <v>1593.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>574.0</v>
+        <v>674.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1842,7 +1842,7 @@
         <v>58</v>
       </c>
       <c r="F62" t="n">
-        <v>249.0</v>
+        <v>271.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1868,7 +1868,7 @@
         <v>58</v>
       </c>
       <c r="F63" t="n">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1946,7 +1946,7 @@
         <v>59</v>
       </c>
       <c r="F66" t="n">
-        <v>331.0</v>
+        <v>334.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1972,7 +1972,7 @@
         <v>59</v>
       </c>
       <c r="F67" t="n">
-        <v>2387.0</v>
+        <v>2402.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1998,7 +1998,7 @@
         <v>59</v>
       </c>
       <c r="F68" t="n">
-        <v>653.0</v>
+        <v>654.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1201.0</v>
+        <v>1207.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2362,7 +2362,7 @@
         <v>59</v>
       </c>
       <c r="F82" t="n">
-        <v>3005.0</v>
+        <v>3012.0</v>
       </c>
       <c r="G82" t="n">
         <v>2.0</v>
@@ -2388,7 +2388,7 @@
         <v>59</v>
       </c>
       <c r="F83" t="n">
-        <v>4623.0</v>
+        <v>4626.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2648,7 +2648,7 @@
         <v>59</v>
       </c>
       <c r="F93" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G93" t="n">
         <v>0.0</v>
@@ -2830,7 +2830,7 @@
         <v>59</v>
       </c>
       <c r="F100" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>
@@ -3012,7 +3012,7 @@
         <v>59</v>
       </c>
       <c r="F107" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13323.0</v>
+        <v>13338.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>
@@ -3324,7 +3324,7 @@
         <v>59</v>
       </c>
       <c r="F119" t="n">
-        <v>1180.0</v>
+        <v>1183.0</v>
       </c>
       <c r="G119" t="n">
         <v>1.0</v>
@@ -3428,7 +3428,7 @@
         <v>59</v>
       </c>
       <c r="F123" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -412,7 +412,7 @@
         <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>1264.0</v>
+        <v>1312.0</v>
       </c>
       <c r="G7" t="n">
         <v>3.0</v>
@@ -464,7 +464,7 @@
         <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>1482.0</v>
+        <v>1485.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11116.0</v>
+        <v>11124.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3677.0</v>
+        <v>3686.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,7 +854,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6919.0</v>
+        <v>6991.0</v>
       </c>
       <c r="G24" t="n">
         <v>45.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8743.0</v>
+        <v>8746.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5385.0</v>
+        <v>5390.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2150.0</v>
+        <v>2153.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1270,7 +1270,7 @@
         <v>58</v>
       </c>
       <c r="F40" t="n">
-        <v>1238.0</v>
+        <v>1241.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1400,7 +1400,7 @@
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>642.0</v>
+        <v>665.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>1822.0</v>
+        <v>1827.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1744.0</v>
+        <v>1746.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1367.0</v>
+        <v>1371.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1738,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1593.0</v>
+        <v>1594.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>674.0</v>
+        <v>690.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1842,7 +1842,7 @@
         <v>58</v>
       </c>
       <c r="F62" t="n">
-        <v>271.0</v>
+        <v>277.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1207.0</v>
+        <v>1208.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2258,7 +2258,7 @@
         <v>59</v>
       </c>
       <c r="F78" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2466,7 +2466,7 @@
         <v>59</v>
       </c>
       <c r="F86" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G86" t="n">
         <v>3.0</v>
@@ -2570,7 +2570,7 @@
         <v>59</v>
       </c>
       <c r="F90" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13338.0</v>
+        <v>13361.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -620,7 +620,7 @@
         <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>517.0</v>
+        <v>523.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -1036,7 +1036,7 @@
         <v>58</v>
       </c>
       <c r="F31" t="n">
-        <v>2153.0</v>
+        <v>2171.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1244,7 +1244,7 @@
         <v>58</v>
       </c>
       <c r="F39" t="n">
-        <v>1477.0</v>
+        <v>1481.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>690.0</v>
+        <v>704.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -2232,7 +2232,7 @@
         <v>59</v>
       </c>
       <c r="F77" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2830,7 +2830,7 @@
         <v>59</v>
       </c>
       <c r="F100" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G100" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -412,7 +412,7 @@
         <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>1312.0</v>
+        <v>1313.0</v>
       </c>
       <c r="G7" t="n">
         <v>3.0</v>
@@ -490,7 +490,7 @@
         <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>1927.0</v>
+        <v>1929.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="F22" t="n">
-        <v>11124.0</v>
+        <v>11168.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -828,7 +828,7 @@
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>3686.0</v>
+        <v>3691.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -854,7 +854,7 @@
         <v>58</v>
       </c>
       <c r="F24" t="n">
-        <v>6991.0</v>
+        <v>7015.0</v>
       </c>
       <c r="G24" t="n">
         <v>45.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8746.0</v>
+        <v>8754.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -932,7 +932,7 @@
         <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>3559.0</v>
+        <v>3560.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5390.0</v>
+        <v>5392.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>1827.0</v>
+        <v>1829.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1746.0</v>
+        <v>1749.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>2838.0</v>
+        <v>2840.0</v>
       </c>
       <c r="G56" t="n">
         <v>8.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1208.0</v>
+        <v>1215.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2622,7 +2622,7 @@
         <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>375.0</v>
+        <v>376.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13361.0</v>
+        <v>13371.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>
@@ -3272,7 +3272,7 @@
         <v>59</v>
       </c>
       <c r="F117" t="n">
-        <v>637.0</v>
+        <v>638.0</v>
       </c>
       <c r="G117" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -308,7 +308,7 @@
         <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>377.0</v>
+        <v>382.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -360,7 +360,7 @@
         <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -386,7 +386,7 @@
         <v>58</v>
       </c>
       <c r="F6" t="n">
-        <v>787.0</v>
+        <v>801.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -438,7 +438,7 @@
         <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>774.0</v>
+        <v>775.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -516,7 +516,7 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>656.0</v>
+        <v>657.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -672,7 +672,7 @@
         <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>507.0</v>
+        <v>510.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
@@ -698,10 +698,10 @@
         <v>58</v>
       </c>
       <c r="F18" t="n">
-        <v>3913.0</v>
+        <v>3920.0</v>
       </c>
       <c r="G18" t="n">
-        <v>116.0</v>
+        <v>120.0</v>
       </c>
       <c r="H18" t="n">
         <v>422.0</v>
@@ -724,13 +724,13 @@
         <v>58</v>
       </c>
       <c r="F19" t="n">
-        <v>1772.0</v>
+        <v>1775.0</v>
       </c>
       <c r="G19" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="H19" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
     </row>
     <row r="20">
@@ -776,7 +776,7 @@
         <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>701.0</v>
+        <v>708.0</v>
       </c>
       <c r="G21" t="n">
         <v>22.0</v>
@@ -880,7 +880,7 @@
         <v>58</v>
       </c>
       <c r="F25" t="n">
-        <v>3672.0</v>
+        <v>3673.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -906,7 +906,7 @@
         <v>58</v>
       </c>
       <c r="F26" t="n">
-        <v>8754.0</v>
+        <v>8784.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -958,7 +958,7 @@
         <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>5392.0</v>
+        <v>5394.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -984,7 +984,7 @@
         <v>58</v>
       </c>
       <c r="F29" t="n">
-        <v>1739.0</v>
+        <v>1741.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1088,10 +1088,10 @@
         <v>58</v>
       </c>
       <c r="F33" t="n">
-        <v>128.0</v>
+        <v>140.0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H33" t="n">
         <v>2.0</v>
@@ -1296,7 +1296,7 @@
         <v>58</v>
       </c>
       <c r="F41" t="n">
-        <v>682.0</v>
+        <v>704.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1322,7 +1322,7 @@
         <v>58</v>
       </c>
       <c r="F42" t="n">
-        <v>443.0</v>
+        <v>458.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1374,7 +1374,7 @@
         <v>58</v>
       </c>
       <c r="F44" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1400,7 +1400,7 @@
         <v>58</v>
       </c>
       <c r="F45" t="n">
-        <v>665.0</v>
+        <v>671.0</v>
       </c>
       <c r="G45" t="n">
         <v>3.0</v>
@@ -1452,7 +1452,7 @@
         <v>58</v>
       </c>
       <c r="F47" t="n">
-        <v>166.0</v>
+        <v>169.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1504,7 +1504,7 @@
         <v>58</v>
       </c>
       <c r="F49" t="n">
-        <v>709.0</v>
+        <v>717.0</v>
       </c>
       <c r="G49" t="n">
         <v>3.0</v>
@@ -1530,7 +1530,7 @@
         <v>58</v>
       </c>
       <c r="F50" t="n">
-        <v>1623.0</v>
+        <v>1630.0</v>
       </c>
       <c r="G50" t="n">
         <v>4.0</v>
@@ -1556,7 +1556,7 @@
         <v>58</v>
       </c>
       <c r="F51" t="n">
-        <v>771.0</v>
+        <v>772.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1582,7 +1582,7 @@
         <v>58</v>
       </c>
       <c r="F52" t="n">
-        <v>1829.0</v>
+        <v>1837.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1608,7 +1608,7 @@
         <v>58</v>
       </c>
       <c r="F53" t="n">
-        <v>1749.0</v>
+        <v>1754.0</v>
       </c>
       <c r="G53" t="n">
         <v>2.0</v>
@@ -1660,7 +1660,7 @@
         <v>58</v>
       </c>
       <c r="F55" t="n">
-        <v>1371.0</v>
+        <v>1381.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="F56" t="n">
-        <v>2840.0</v>
+        <v>2842.0</v>
       </c>
       <c r="G56" t="n">
         <v>8.0</v>
@@ -1738,7 +1738,7 @@
         <v>58</v>
       </c>
       <c r="F58" t="n">
-        <v>1594.0</v>
+        <v>1595.0</v>
       </c>
       <c r="G58" t="n">
         <v>2.0</v>
@@ -1790,7 +1790,7 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>704.0</v>
+        <v>724.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1946,7 +1946,7 @@
         <v>59</v>
       </c>
       <c r="F66" t="n">
-        <v>334.0</v>
+        <v>345.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1972,7 +1972,7 @@
         <v>59</v>
       </c>
       <c r="F67" t="n">
-        <v>2402.0</v>
+        <v>2414.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1998,7 +1998,7 @@
         <v>59</v>
       </c>
       <c r="F68" t="n">
-        <v>654.0</v>
+        <v>662.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2024,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="F69" t="n">
-        <v>187.0</v>
+        <v>194.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2102,7 +2102,7 @@
         <v>59</v>
       </c>
       <c r="F72" t="n">
-        <v>2319.0</v>
+        <v>2330.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2180,7 +2180,7 @@
         <v>59</v>
       </c>
       <c r="F75" t="n">
-        <v>1215.0</v>
+        <v>1216.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2336,7 +2336,7 @@
         <v>59</v>
       </c>
       <c r="F81" t="n">
-        <v>105.0</v>
+        <v>107.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2362,7 +2362,7 @@
         <v>59</v>
       </c>
       <c r="F82" t="n">
-        <v>3012.0</v>
+        <v>3044.0</v>
       </c>
       <c r="G82" t="n">
         <v>2.0</v>
@@ -2388,7 +2388,7 @@
         <v>59</v>
       </c>
       <c r="F83" t="n">
-        <v>4626.0</v>
+        <v>4652.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -2414,7 +2414,7 @@
         <v>59</v>
       </c>
       <c r="F84" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2622,7 +2622,7 @@
         <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>376.0</v>
+        <v>377.0</v>
       </c>
       <c r="G92" t="n">
         <v>1.0</v>
@@ -2960,7 +2960,7 @@
         <v>59</v>
       </c>
       <c r="F105" t="n">
-        <v>293.0</v>
+        <v>296.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -3064,7 +3064,7 @@
         <v>59</v>
       </c>
       <c r="F109" t="n">
-        <v>4011.0</v>
+        <v>4012.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3090,7 +3090,7 @@
         <v>59</v>
       </c>
       <c r="F110" t="n">
-        <v>7963.0</v>
+        <v>7964.0</v>
       </c>
       <c r="G110" t="n">
         <v>1.0</v>
@@ -3246,7 +3246,7 @@
         <v>59</v>
       </c>
       <c r="F116" t="n">
-        <v>13371.0</v>
+        <v>13373.0</v>
       </c>
       <c r="G116" t="n">
         <v>13.0</v>
@@ -3376,7 +3376,7 @@
         <v>59</v>
       </c>
       <c r="F121" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="61">
   <si>
     <t>Area</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Massa-carrara</t>
+  </si>
+  <si>
+    <t>Imperia</t>
   </si>
   <si>
     <t>Brescia</t>
@@ -279,7 +282,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
         <v>173.0</v>
@@ -305,7 +308,7 @@
         <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
         <v>382.0</v>
@@ -331,7 +334,7 @@
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F4" t="n">
         <v>192.0</v>
@@ -357,7 +360,7 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
         <v>330.0</v>
@@ -383,7 +386,7 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
         <v>801.0</v>
@@ -409,10 +412,10 @@
         <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>1313.0</v>
+        <v>1351.0</v>
       </c>
       <c r="G7" t="n">
         <v>3.0</v>
@@ -435,7 +438,7 @@
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
         <v>775.0</v>
@@ -461,7 +464,7 @@
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
         <v>1485.0</v>
@@ -487,10 +490,10 @@
         <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>1929.0</v>
+        <v>1942.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -513,10 +516,10 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>657.0</v>
+        <v>674.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -539,7 +542,7 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
         <v>9.0</v>
@@ -565,10 +568,10 @@
         <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -591,10 +594,10 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="G14" t="n">
         <v>2.0</v>
@@ -617,10 +620,10 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>523.0</v>
+        <v>532.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -643,10 +646,10 @@
         <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>104.0</v>
+        <v>114.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -669,7 +672,7 @@
         <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F17" t="n">
         <v>510.0</v>
@@ -695,7 +698,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
         <v>3920.0</v>
@@ -721,7 +724,7 @@
         <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F19" t="n">
         <v>1775.0</v>
@@ -747,7 +750,7 @@
         <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -773,7 +776,7 @@
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
         <v>708.0</v>
@@ -799,10 +802,10 @@
         <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11168.0</v>
+        <v>11232.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -825,10 +828,10 @@
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3691.0</v>
+        <v>3727.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -851,10 +854,10 @@
         <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7015.0</v>
+        <v>7081.0</v>
       </c>
       <c r="G24" t="n">
         <v>45.0</v>
@@ -877,7 +880,7 @@
         <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F25" t="n">
         <v>3673.0</v>
@@ -903,7 +906,7 @@
         <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F26" t="n">
         <v>8784.0</v>
@@ -929,10 +932,10 @@
         <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3560.0</v>
+        <v>3590.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -955,10 +958,10 @@
         <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5394.0</v>
+        <v>5438.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -981,10 +984,10 @@
         <v>33</v>
       </c>
       <c r="E29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>1741.0</v>
+        <v>1745.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1007,7 +1010,7 @@
         <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -1033,10 +1036,10 @@
         <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2171.0</v>
+        <v>2222.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1059,7 +1062,7 @@
         <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="n">
         <v>6.0</v>
@@ -1085,7 +1088,7 @@
         <v>22</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F33" t="n">
         <v>140.0</v>
@@ -1111,7 +1114,7 @@
         <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F34" t="n">
         <v>69.0</v>
@@ -1137,7 +1140,7 @@
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F35" t="n">
         <v>15.0</v>
@@ -1163,7 +1166,7 @@
         <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F36" t="n">
         <v>3.0</v>
@@ -1189,7 +1192,7 @@
         <v>33</v>
       </c>
       <c r="E37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F37" t="n">
         <v>101.0</v>
@@ -1215,7 +1218,7 @@
         <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F38" t="n">
         <v>0.0</v>
@@ -1241,10 +1244,10 @@
         <v>41</v>
       </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>1481.0</v>
+        <v>1510.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1267,10 +1270,10 @@
         <v>35</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F40" t="n">
-        <v>1241.0</v>
+        <v>1242.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1293,7 +1296,7 @@
         <v>22</v>
       </c>
       <c r="E41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
         <v>704.0</v>
@@ -1319,7 +1322,7 @@
         <v>23</v>
       </c>
       <c r="E42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F42" t="n">
         <v>458.0</v>
@@ -1345,7 +1348,7 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F43" t="n">
         <v>42.0</v>
@@ -1371,7 +1374,7 @@
         <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F44" t="n">
         <v>126.0</v>
@@ -1394,16 +1397,16 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F45" t="n">
-        <v>671.0</v>
+        <v>1.0</v>
       </c>
       <c r="G45" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1417,19 +1420,19 @@
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0</v>
+        <v>671.0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1449,10 +1452,10 @@
         <v>43</v>
       </c>
       <c r="E47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F47" t="n">
-        <v>169.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1475,13 +1478,13 @@
         <v>44</v>
       </c>
       <c r="E48" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F48" t="n">
-        <v>86.0</v>
+        <v>169.0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1501,16 +1504,16 @@
         <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F49" t="n">
-        <v>717.0</v>
+        <v>86.0</v>
       </c>
       <c r="G49" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H49" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -1524,19 +1527,19 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F50" t="n">
-        <v>1630.0</v>
+        <v>717.0</v>
       </c>
       <c r="G50" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H50" t="n">
-        <v>86.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="51">
@@ -1550,19 +1553,19 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F51" t="n">
-        <v>772.0</v>
+        <v>1630.0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="52">
@@ -1573,22 +1576,22 @@
         <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F52" t="n">
-        <v>1837.0</v>
+        <v>772.0</v>
       </c>
       <c r="G52" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -1602,19 +1605,19 @@
         <v>16</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>1754.0</v>
+        <v>1837.0</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="54">
@@ -1628,16 +1631,16 @@
         <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1.0</v>
+        <v>1782.0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1654,16 +1657,16 @@
         <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F55" t="n">
-        <v>1381.0</v>
+        <v>1.0</v>
       </c>
       <c r="G55" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1680,19 +1683,19 @@
         <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>2842.0</v>
+        <v>1397.0</v>
       </c>
       <c r="G56" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H56" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
@@ -1709,16 +1712,16 @@
         <v>49</v>
       </c>
       <c r="E57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F57" t="n">
-        <v>2.0</v>
+        <v>2842.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="58">
@@ -1735,13 +1738,13 @@
         <v>50</v>
       </c>
       <c r="E58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F58" t="n">
-        <v>1595.0</v>
+        <v>2.0</v>
       </c>
       <c r="G58" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
         <v>0.0</v>
@@ -1755,19 +1758,19 @@
         <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D59" t="s">
         <v>51</v>
       </c>
       <c r="E59" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F59" t="n">
+        <v>1595.0</v>
+      </c>
+      <c r="G59" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1784,13 +1787,13 @@
         <v>17</v>
       </c>
       <c r="D60" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F60" t="n">
-        <v>724.0</v>
+        <v>2.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1810,13 +1813,13 @@
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>1.0</v>
+        <v>756.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1836,13 +1839,13 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>277.0</v>
+        <v>1.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1862,13 +1865,13 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F63" t="n">
-        <v>27.0</v>
+        <v>283.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1888,13 +1891,13 @@
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>1.0</v>
+        <v>32.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1908,19 +1911,19 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="E65" t="s">
         <v>59</v>
       </c>
       <c r="F65" t="n">
-        <v>38.0</v>
+        <v>1.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1940,13 +1943,13 @@
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F66" t="n">
-        <v>345.0</v>
+        <v>38.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1966,13 +1969,13 @@
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F67" t="n">
-        <v>2414.0</v>
+        <v>345.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1992,13 +1995,13 @@
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>662.0</v>
+        <v>2414.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2018,13 +2021,13 @@
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>194.0</v>
+        <v>662.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2041,16 +2044,16 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>9.0</v>
+        <v>194.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2067,16 +2070,16 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F71" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2096,19 +2099,19 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E72" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F72" t="n">
-        <v>2330.0</v>
+        <v>1.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
       </c>
       <c r="H72" t="n">
-        <v>12778.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -2119,22 +2122,22 @@
         <v>9</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F73" t="n">
-        <v>853.0</v>
+        <v>2330.0</v>
       </c>
       <c r="G73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0</v>
+        <v>12778.0</v>
       </c>
     </row>
     <row r="74">
@@ -2148,16 +2151,16 @@
         <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E74" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F74" t="n">
-        <v>136.0</v>
+        <v>853.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2174,16 +2177,16 @@
         <v>16</v>
       </c>
       <c r="D75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E75" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F75" t="n">
-        <v>1216.0</v>
+        <v>136.0</v>
       </c>
       <c r="G75" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2197,19 +2200,19 @@
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>13.0</v>
+        <v>1222.0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2226,13 +2229,13 @@
         <v>17</v>
       </c>
       <c r="D77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F77" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2252,13 +2255,13 @@
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F78" t="n">
-        <v>28.0</v>
+        <v>9.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
@@ -2278,13 +2281,13 @@
         <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F79" t="n">
-        <v>18.0</v>
+        <v>28.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2298,19 +2301,19 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F80" t="n">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2327,16 +2330,16 @@
         <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D81" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="E81" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F81" t="n">
-        <v>107.0</v>
+        <v>2.0</v>
       </c>
       <c r="G81" t="n">
         <v>0.0</v>
@@ -2356,16 +2359,16 @@
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E82" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F82" t="n">
-        <v>3044.0</v>
+        <v>107.0</v>
       </c>
       <c r="G82" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2382,19 +2385,19 @@
         <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>4652.0</v>
+        <v>3044.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H83" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -2408,19 +2411,19 @@
         <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F84" t="n">
-        <v>59.0</v>
+        <v>4652.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
       </c>
       <c r="H84" t="n">
-        <v>0.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="85">
@@ -2431,16 +2434,16 @@
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F85" t="n">
-        <v>32.0</v>
+        <v>59.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2460,16 +2463,16 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E86" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F86" t="n">
-        <v>25.0</v>
+        <v>32.0</v>
       </c>
       <c r="G86" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2486,16 +2489,16 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E87" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F87" t="n">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H87" t="n">
         <v>0.0</v>
@@ -2509,16 +2512,16 @@
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E88" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F88" t="n">
-        <v>9.0</v>
+        <v>30.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2538,19 +2541,19 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F89" t="n">
-        <v>74.0</v>
+        <v>9.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>130.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2561,22 +2564,22 @@
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F90" t="n">
-        <v>259.0</v>
+        <v>74.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="91">
@@ -2590,13 +2593,13 @@
         <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>5.0</v>
+        <v>259.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2616,16 +2619,16 @@
         <v>16</v>
       </c>
       <c r="D92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E92" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F92" t="n">
-        <v>377.0</v>
+        <v>5.0</v>
       </c>
       <c r="G92" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H92" t="n">
         <v>0.0</v>
@@ -2639,19 +2642,19 @@
         <v>10</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D93" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>30.0</v>
+        <v>378.0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2668,13 +2671,13 @@
         <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E94" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F94" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="G94" t="n">
         <v>0.0</v>
@@ -2688,19 +2691,19 @@
         <v>8</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C95" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D95" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E95" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F95" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G95" t="n">
         <v>0.0</v>
@@ -2720,13 +2723,13 @@
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E96" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F96" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2743,16 +2746,16 @@
         <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F97" t="n">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2772,19 +2775,19 @@
         <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E98" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F98" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
       </c>
       <c r="H98" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -2798,19 +2801,19 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E99" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F99" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="100">
@@ -2824,19 +2827,19 @@
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E100" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F100" t="n">
-        <v>43.0</v>
+        <v>9.0</v>
       </c>
       <c r="G100" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="101">
@@ -2844,25 +2847,25 @@
         <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E101" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F101" t="n">
-        <v>13.0</v>
+        <v>43.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H101" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="102">
@@ -2873,16 +2876,16 @@
         <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D102" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E102" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F102" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
       <c r="G102" t="n">
         <v>0.0</v>
@@ -2899,16 +2902,16 @@
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E103" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F103" t="n">
-        <v>244.0</v>
+        <v>3.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2928,13 +2931,13 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E104" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F104" t="n">
-        <v>540.0</v>
+        <v>244.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2954,13 +2957,13 @@
         <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E105" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F105" t="n">
-        <v>296.0</v>
+        <v>540.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2980,13 +2983,13 @@
         <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E106" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F106" t="n">
-        <v>1.0</v>
+        <v>296.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -3006,13 +3009,13 @@
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F107" t="n">
-        <v>306.0</v>
+        <v>1.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3029,16 +3032,16 @@
         <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E108" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F108" t="n">
-        <v>13.0</v>
+        <v>306.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3055,16 +3058,16 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E109" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F109" t="n">
-        <v>4012.0</v>
+        <v>13.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3087,16 +3090,16 @@
         <v>44</v>
       </c>
       <c r="E110" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F110" t="n">
-        <v>7964.0</v>
+        <v>4012.0</v>
       </c>
       <c r="G110" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H110" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="111">
@@ -3113,16 +3116,16 @@
         <v>45</v>
       </c>
       <c r="E111" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F111" t="n">
-        <v>1229.0</v>
+        <v>7964.0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H111" t="n">
-        <v>670.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="112">
@@ -3136,19 +3139,19 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E112" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F112" t="n">
-        <v>3880.0</v>
+        <v>1229.0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H112" t="n">
-        <v>23.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="113">
@@ -3162,19 +3165,19 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="E113" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F113" t="n">
-        <v>78.0</v>
+        <v>3880.0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H113" t="n">
-        <v>0.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="114">
@@ -3185,22 +3188,22 @@
         <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E114" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F114" t="n">
-        <v>340.0</v>
+        <v>78.0</v>
       </c>
       <c r="G114" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H114" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="115">
@@ -3214,19 +3217,19 @@
         <v>16</v>
       </c>
       <c r="D115" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E115" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F115" t="n">
-        <v>153.0</v>
+        <v>340.0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H115" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="116">
@@ -3240,16 +3243,16 @@
         <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E116" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F116" t="n">
-        <v>13373.0</v>
+        <v>153.0</v>
       </c>
       <c r="G116" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H116" t="n">
         <v>0.0</v>
@@ -3266,19 +3269,19 @@
         <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E117" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>638.0</v>
+        <v>13399.0</v>
       </c>
       <c r="G117" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="H117" t="n">
-        <v>66.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="118">
@@ -3295,16 +3298,16 @@
         <v>49</v>
       </c>
       <c r="E118" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>4.0</v>
+        <v>638.0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H118" t="n">
-        <v>0.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="119">
@@ -3321,16 +3324,16 @@
         <v>50</v>
       </c>
       <c r="E119" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F119" t="n">
-        <v>1183.0</v>
+        <v>4.0</v>
       </c>
       <c r="G119" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H119" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="120">
@@ -3341,22 +3344,22 @@
         <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E120" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F120" t="n">
+        <v>1184.0</v>
+      </c>
+      <c r="G120" t="n">
         <v>1.0</v>
       </c>
-      <c r="G120" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H120" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="121">
@@ -3367,16 +3370,16 @@
         <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E121" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F121" t="n">
-        <v>140.0</v>
+        <v>1.0</v>
       </c>
       <c r="G121" t="n">
         <v>0.0</v>
@@ -3396,13 +3399,13 @@
         <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E122" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F122" t="n">
-        <v>1.0</v>
+        <v>141.0</v>
       </c>
       <c r="G122" t="n">
         <v>0.0</v>
@@ -3422,13 +3425,13 @@
         <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E123" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F123" t="n">
-        <v>51.0</v>
+        <v>1.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>
@@ -3445,21 +3448,47 @@
         <v>12</v>
       </c>
       <c r="C124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" t="s">
+        <v>34</v>
+      </c>
+      <c r="E124" t="s">
+        <v>60</v>
+      </c>
+      <c r="F124" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>8</v>
+      </c>
+      <c r="B125" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" t="s">
         <v>21</v>
       </c>
-      <c r="D124" t="s">
-        <v>57</v>
-      </c>
-      <c r="E124" t="s">
-        <v>59</v>
-      </c>
-      <c r="F124" t="n">
+      <c r="D125" t="s">
+        <v>58</v>
+      </c>
+      <c r="E125" t="s">
+        <v>60</v>
+      </c>
+      <c r="F125" t="n">
         <v>5.0</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H124" t="n">
+      <c r="G125" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H125" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -467,7 +467,7 @@
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>1485.0</v>
+        <v>1493.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -493,7 +493,7 @@
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>1942.0</v>
+        <v>1943.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -519,7 +519,7 @@
         <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>674.0</v>
+        <v>676.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -701,10 +701,10 @@
         <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>3920.0</v>
+        <v>3922.0</v>
       </c>
       <c r="G18" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="H18" t="n">
         <v>422.0</v>
@@ -727,7 +727,7 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>1775.0</v>
+        <v>1776.0</v>
       </c>
       <c r="G19" t="n">
         <v>56.0</v>
@@ -779,7 +779,7 @@
         <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>708.0</v>
+        <v>710.0</v>
       </c>
       <c r="G21" t="n">
         <v>22.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8784.0</v>
+        <v>8811.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3590.0</v>
+        <v>3591.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5438.0</v>
+        <v>5441.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -987,7 +987,7 @@
         <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>1745.0</v>
+        <v>1750.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2222.0</v>
+        <v>2226.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1091,7 +1091,7 @@
         <v>59</v>
       </c>
       <c r="F33" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="G33" t="n">
         <v>1.0</v>
@@ -1247,7 +1247,7 @@
         <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>1510.0</v>
+        <v>1511.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1273,7 +1273,7 @@
         <v>59</v>
       </c>
       <c r="F40" t="n">
-        <v>1242.0</v>
+        <v>1248.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1299,7 +1299,7 @@
         <v>59</v>
       </c>
       <c r="F41" t="n">
-        <v>704.0</v>
+        <v>710.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1611,7 +1611,7 @@
         <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>1837.0</v>
+        <v>1852.0</v>
       </c>
       <c r="G53" t="n">
         <v>4.0</v>
@@ -1637,7 +1637,7 @@
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1782.0</v>
+        <v>1788.0</v>
       </c>
       <c r="G54" t="n">
         <v>2.0</v>
@@ -1689,7 +1689,7 @@
         <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>1397.0</v>
+        <v>1407.0</v>
       </c>
       <c r="G56" t="n">
         <v>6.0</v>
@@ -1819,7 +1819,7 @@
         <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>756.0</v>
+        <v>821.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1871,7 +1871,7 @@
         <v>59</v>
       </c>
       <c r="F63" t="n">
-        <v>283.0</v>
+        <v>301.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1975,7 +1975,7 @@
         <v>60</v>
       </c>
       <c r="F67" t="n">
-        <v>345.0</v>
+        <v>350.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2001,7 +2001,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>2414.0</v>
+        <v>2418.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2027,7 +2027,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>662.0</v>
+        <v>666.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2053,7 +2053,7 @@
         <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>194.0</v>
+        <v>204.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1222.0</v>
+        <v>1228.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2287,7 +2287,7 @@
         <v>60</v>
       </c>
       <c r="F79" t="n">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2365,7 +2365,7 @@
         <v>60</v>
       </c>
       <c r="F82" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2391,7 +2391,7 @@
         <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>3044.0</v>
+        <v>3045.0</v>
       </c>
       <c r="G83" t="n">
         <v>2.0</v>
@@ -2417,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="F84" t="n">
-        <v>4652.0</v>
+        <v>4672.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2599,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2963,7 +2963,7 @@
         <v>60</v>
       </c>
       <c r="F105" t="n">
-        <v>540.0</v>
+        <v>541.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -3275,7 +3275,7 @@
         <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>13399.0</v>
+        <v>13414.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>
@@ -3405,7 +3405,7 @@
         <v>60</v>
       </c>
       <c r="F122" t="n">
-        <v>141.0</v>
+        <v>144.0</v>
       </c>
       <c r="G122" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -545,7 +545,7 @@
         <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -597,7 +597,7 @@
         <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>231.0</v>
+        <v>232.0</v>
       </c>
       <c r="G14" t="n">
         <v>2.0</v>
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3727.0</v>
+        <v>3735.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8811.0</v>
+        <v>8823.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3591.0</v>
+        <v>3593.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,13 +961,13 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5441.0</v>
+        <v>5449.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
       </c>
       <c r="H28" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="29">
@@ -1019,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="31">
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2226.0</v>
+        <v>2227.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1429,7 +1429,7 @@
         <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>671.0</v>
+        <v>693.0</v>
       </c>
       <c r="G46" t="n">
         <v>3.0</v>
@@ -1611,7 +1611,7 @@
         <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>1852.0</v>
+        <v>1856.0</v>
       </c>
       <c r="G53" t="n">
         <v>4.0</v>
@@ -1689,7 +1689,7 @@
         <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>1407.0</v>
+        <v>1411.0</v>
       </c>
       <c r="G56" t="n">
         <v>6.0</v>
@@ -2157,7 +2157,7 @@
         <v>60</v>
       </c>
       <c r="F74" t="n">
-        <v>853.0</v>
+        <v>854.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1228.0</v>
+        <v>1229.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2599,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>638.0</v>
+        <v>639.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -649,7 +649,7 @@
         <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>114.0</v>
+        <v>116.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2227.0</v>
+        <v>2236.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1247,7 +1247,7 @@
         <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>1511.0</v>
+        <v>1519.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1273,7 +1273,7 @@
         <v>59</v>
       </c>
       <c r="F40" t="n">
-        <v>1248.0</v>
+        <v>1250.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1819,7 +1819,7 @@
         <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>821.0</v>
+        <v>829.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -415,10 +415,10 @@
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>1351.0</v>
+        <v>1388.0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H7" t="n">
         <v>0.0</v>
@@ -467,7 +467,7 @@
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>1493.0</v>
+        <v>1494.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -493,7 +493,7 @@
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>1943.0</v>
+        <v>1945.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -519,7 +519,7 @@
         <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>676.0</v>
+        <v>697.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -805,7 +805,7 @@
         <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11232.0</v>
+        <v>11287.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3735.0</v>
+        <v>3742.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -857,10 +857,10 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7081.0</v>
+        <v>7143.0</v>
       </c>
       <c r="G24" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="H24" t="n">
         <v>275.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8823.0</v>
+        <v>8828.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3593.0</v>
+        <v>3600.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5449.0</v>
+        <v>5474.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2236.0</v>
+        <v>2237.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1429,7 +1429,7 @@
         <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>693.0</v>
+        <v>694.0</v>
       </c>
       <c r="G46" t="n">
         <v>3.0</v>
@@ -1637,7 +1637,7 @@
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1788.0</v>
+        <v>1798.0</v>
       </c>
       <c r="G54" t="n">
         <v>2.0</v>
@@ -1663,7 +1663,7 @@
         <v>59</v>
       </c>
       <c r="F55" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G55" t="n">
         <v>0.0</v>
@@ -1689,7 +1689,7 @@
         <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>1411.0</v>
+        <v>1434.0</v>
       </c>
       <c r="G56" t="n">
         <v>6.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1229.0</v>
+        <v>1234.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2651,7 +2651,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -3275,7 +3275,7 @@
         <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>13414.0</v>
+        <v>13432.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>639.0</v>
+        <v>640.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -3353,7 +3353,7 @@
         <v>60</v>
       </c>
       <c r="F120" t="n">
-        <v>1184.0</v>
+        <v>1190.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -441,7 +441,7 @@
         <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>775.0</v>
+        <v>783.0</v>
       </c>
       <c r="G8" t="n">
         <v>2.0</v>
@@ -519,7 +519,7 @@
         <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>697.0</v>
+        <v>699.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -863,7 +863,7 @@
         <v>46.0</v>
       </c>
       <c r="H24" t="n">
-        <v>275.0</v>
+        <v>276.0</v>
       </c>
     </row>
     <row r="25">
@@ -883,7 +883,7 @@
         <v>59</v>
       </c>
       <c r="F25" t="n">
-        <v>3673.0</v>
+        <v>3679.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8828.0</v>
+        <v>8842.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3600.0</v>
+        <v>3605.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5474.0</v>
+        <v>5475.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -1429,7 +1429,7 @@
         <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>694.0</v>
+        <v>721.0</v>
       </c>
       <c r="G46" t="n">
         <v>3.0</v>
@@ -1481,7 +1481,7 @@
         <v>59</v>
       </c>
       <c r="F48" t="n">
-        <v>169.0</v>
+        <v>174.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1559,7 +1559,7 @@
         <v>59</v>
       </c>
       <c r="F51" t="n">
-        <v>1630.0</v>
+        <v>1636.0</v>
       </c>
       <c r="G51" t="n">
         <v>4.0</v>
@@ -1585,7 +1585,7 @@
         <v>59</v>
       </c>
       <c r="F52" t="n">
-        <v>772.0</v>
+        <v>775.0</v>
       </c>
       <c r="G52" t="n">
         <v>0.0</v>
@@ -1611,7 +1611,7 @@
         <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>1856.0</v>
+        <v>1858.0</v>
       </c>
       <c r="G53" t="n">
         <v>4.0</v>
@@ -1689,7 +1689,7 @@
         <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>1434.0</v>
+        <v>1436.0</v>
       </c>
       <c r="G56" t="n">
         <v>6.0</v>
@@ -1819,7 +1819,7 @@
         <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>829.0</v>
+        <v>832.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -2131,7 +2131,7 @@
         <v>60</v>
       </c>
       <c r="F73" t="n">
-        <v>2330.0</v>
+        <v>2341.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1234.0</v>
+        <v>1239.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2599,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>261.0</v>
+        <v>263.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -3093,7 +3093,7 @@
         <v>60</v>
       </c>
       <c r="F110" t="n">
-        <v>4012.0</v>
+        <v>4013.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3119,7 +3119,7 @@
         <v>60</v>
       </c>
       <c r="F111" t="n">
-        <v>7964.0</v>
+        <v>7966.0</v>
       </c>
       <c r="G111" t="n">
         <v>1.0</v>
@@ -3197,7 +3197,7 @@
         <v>60</v>
       </c>
       <c r="F114" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G114" t="n">
         <v>0.0</v>
@@ -3275,7 +3275,7 @@
         <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>13432.0</v>
+        <v>13444.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -415,7 +415,7 @@
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>1388.0</v>
+        <v>1400.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -467,7 +467,7 @@
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>1494.0</v>
+        <v>1496.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -493,7 +493,7 @@
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>1945.0</v>
+        <v>1960.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -519,7 +519,7 @@
         <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>699.0</v>
+        <v>716.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -623,7 +623,7 @@
         <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>532.0</v>
+        <v>535.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -649,7 +649,7 @@
         <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>116.0</v>
+        <v>133.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -707,7 +707,7 @@
         <v>121.0</v>
       </c>
       <c r="H18" t="n">
-        <v>422.0</v>
+        <v>423.0</v>
       </c>
     </row>
     <row r="19">
@@ -805,7 +805,7 @@
         <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11287.0</v>
+        <v>11321.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3742.0</v>
+        <v>3782.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -857,7 +857,7 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7143.0</v>
+        <v>7198.0</v>
       </c>
       <c r="G24" t="n">
         <v>46.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8842.0</v>
+        <v>8873.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3605.0</v>
+        <v>3614.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5475.0</v>
+        <v>5520.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -993,7 +993,7 @@
         <v>1.0</v>
       </c>
       <c r="H29" t="n">
-        <v>434.0</v>
+        <v>435.0</v>
       </c>
     </row>
     <row r="30">
@@ -1019,7 +1019,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>209.0</v>
+        <v>210.0</v>
       </c>
     </row>
     <row r="31">
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2237.0</v>
+        <v>2256.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1247,7 +1247,7 @@
         <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>1519.0</v>
+        <v>1539.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1273,7 +1273,7 @@
         <v>59</v>
       </c>
       <c r="F40" t="n">
-        <v>1250.0</v>
+        <v>1263.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1611,7 +1611,7 @@
         <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>1858.0</v>
+        <v>1863.0</v>
       </c>
       <c r="G53" t="n">
         <v>4.0</v>
@@ -1637,7 +1637,7 @@
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1798.0</v>
+        <v>1820.0</v>
       </c>
       <c r="G54" t="n">
         <v>2.0</v>
@@ -1689,7 +1689,7 @@
         <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>1436.0</v>
+        <v>1450.0</v>
       </c>
       <c r="G56" t="n">
         <v>6.0</v>
@@ -1819,7 +1819,7 @@
         <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>832.0</v>
+        <v>864.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1871,7 +1871,7 @@
         <v>59</v>
       </c>
       <c r="F63" t="n">
-        <v>301.0</v>
+        <v>306.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1897,7 +1897,7 @@
         <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1239.0</v>
+        <v>1241.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2417,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="F84" t="n">
-        <v>4672.0</v>
+        <v>4675.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2651,7 +2651,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>379.0</v>
+        <v>380.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -3223,7 +3223,7 @@
         <v>60</v>
       </c>
       <c r="F115" t="n">
-        <v>340.0</v>
+        <v>341.0</v>
       </c>
       <c r="G115" t="n">
         <v>1.0</v>
@@ -3275,7 +3275,7 @@
         <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>13444.0</v>
+        <v>13464.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>
@@ -3353,7 +3353,7 @@
         <v>60</v>
       </c>
       <c r="F120" t="n">
-        <v>1190.0</v>
+        <v>1198.0</v>
       </c>
       <c r="G120" t="n">
         <v>1.0</v>
@@ -3405,7 +3405,7 @@
         <v>60</v>
       </c>
       <c r="F122" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="G122" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -285,7 +285,7 @@
         <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -311,7 +311,7 @@
         <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>382.0</v>
+        <v>404.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -337,7 +337,7 @@
         <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>192.0</v>
+        <v>195.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -363,7 +363,7 @@
         <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>330.0</v>
+        <v>333.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>
@@ -389,7 +389,7 @@
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>801.0</v>
+        <v>822.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -415,7 +415,7 @@
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>1400.0</v>
+        <v>1401.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -571,7 +571,7 @@
         <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -623,7 +623,7 @@
         <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>535.0</v>
+        <v>537.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -649,7 +649,7 @@
         <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -675,7 +675,7 @@
         <v>59</v>
       </c>
       <c r="F17" t="n">
-        <v>510.0</v>
+        <v>513.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
@@ -701,10 +701,10 @@
         <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>3922.0</v>
+        <v>3978.0</v>
       </c>
       <c r="G18" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="H18" t="n">
         <v>423.0</v>
@@ -727,7 +727,7 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>1776.0</v>
+        <v>1777.0</v>
       </c>
       <c r="G19" t="n">
         <v>56.0</v>
@@ -779,7 +779,7 @@
         <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>710.0</v>
+        <v>723.0</v>
       </c>
       <c r="G21" t="n">
         <v>22.0</v>
@@ -805,13 +805,13 @@
         <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11321.0</v>
+        <v>11331.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
       </c>
       <c r="H22" t="n">
-        <v>1024.0</v>
+        <v>1025.0</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3782.0</v>
+        <v>3784.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8873.0</v>
+        <v>8874.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3614.0</v>
+        <v>3616.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -987,7 +987,7 @@
         <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>1750.0</v>
+        <v>1775.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2256.0</v>
+        <v>2258.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1091,7 +1091,7 @@
         <v>59</v>
       </c>
       <c r="F33" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G33" t="n">
         <v>1.0</v>
@@ -1247,7 +1247,7 @@
         <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>1539.0</v>
+        <v>1540.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1299,7 +1299,7 @@
         <v>59</v>
       </c>
       <c r="F41" t="n">
-        <v>710.0</v>
+        <v>729.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1325,7 +1325,7 @@
         <v>59</v>
       </c>
       <c r="F42" t="n">
-        <v>458.0</v>
+        <v>490.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1351,7 +1351,7 @@
         <v>59</v>
       </c>
       <c r="F43" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1377,7 +1377,7 @@
         <v>59</v>
       </c>
       <c r="F44" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1429,7 +1429,7 @@
         <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>721.0</v>
+        <v>753.0</v>
       </c>
       <c r="G46" t="n">
         <v>3.0</v>
@@ -1689,7 +1689,7 @@
         <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>1450.0</v>
+        <v>1459.0</v>
       </c>
       <c r="G56" t="n">
         <v>6.0</v>
@@ -1819,7 +1819,7 @@
         <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>864.0</v>
+        <v>949.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1871,7 +1871,7 @@
         <v>59</v>
       </c>
       <c r="F63" t="n">
-        <v>306.0</v>
+        <v>309.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1897,7 +1897,7 @@
         <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1975,7 +1975,7 @@
         <v>60</v>
       </c>
       <c r="F67" t="n">
-        <v>350.0</v>
+        <v>363.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2001,7 +2001,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>2418.0</v>
+        <v>2441.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2027,7 +2027,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>666.0</v>
+        <v>669.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2053,7 +2053,7 @@
         <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>204.0</v>
+        <v>210.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2183,7 +2183,7 @@
         <v>60</v>
       </c>
       <c r="F75" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G75" t="n">
         <v>0.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1241.0</v>
+        <v>1245.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2391,7 +2391,7 @@
         <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>3045.0</v>
+        <v>3073.0</v>
       </c>
       <c r="G83" t="n">
         <v>2.0</v>
@@ -2417,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="F84" t="n">
-        <v>4675.0</v>
+        <v>4699.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2443,7 +2443,7 @@
         <v>60</v>
       </c>
       <c r="F85" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2651,7 +2651,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>380.0</v>
+        <v>381.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -2963,7 +2963,7 @@
         <v>60</v>
       </c>
       <c r="F105" t="n">
-        <v>541.0</v>
+        <v>542.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -3275,7 +3275,7 @@
         <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>13464.0</v>
+        <v>13477.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>640.0</v>
+        <v>642.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>
@@ -3405,7 +3405,7 @@
         <v>60</v>
       </c>
       <c r="F122" t="n">
-        <v>146.0</v>
+        <v>149.0</v>
       </c>
       <c r="G122" t="n">
         <v>0.0</v>
@@ -3457,7 +3457,7 @@
         <v>60</v>
       </c>
       <c r="F124" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G124" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -467,7 +467,7 @@
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>1496.0</v>
+        <v>1498.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -493,7 +493,7 @@
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>1960.0</v>
+        <v>1962.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -857,7 +857,7 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7198.0</v>
+        <v>7204.0</v>
       </c>
       <c r="G24" t="n">
         <v>46.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8874.0</v>
+        <v>8892.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5520.0</v>
+        <v>5524.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -1611,7 +1611,7 @@
         <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>1863.0</v>
+        <v>1866.0</v>
       </c>
       <c r="G53" t="n">
         <v>4.0</v>
@@ -1637,7 +1637,7 @@
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1820.0</v>
+        <v>1831.0</v>
       </c>
       <c r="G54" t="n">
         <v>2.0</v>
@@ -1689,7 +1689,7 @@
         <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>1459.0</v>
+        <v>1479.0</v>
       </c>
       <c r="G56" t="n">
         <v>6.0</v>
@@ -1767,7 +1767,7 @@
         <v>59</v>
       </c>
       <c r="F59" t="n">
-        <v>1595.0</v>
+        <v>1596.0</v>
       </c>
       <c r="G59" t="n">
         <v>2.0</v>
@@ -1897,7 +1897,7 @@
         <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1245.0</v>
+        <v>1248.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -3223,7 +3223,7 @@
         <v>60</v>
       </c>
       <c r="F115" t="n">
-        <v>341.0</v>
+        <v>343.0</v>
       </c>
       <c r="G115" t="n">
         <v>1.0</v>
@@ -3275,7 +3275,7 @@
         <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>13477.0</v>
+        <v>13497.0</v>
       </c>
       <c r="G117" t="n">
         <v>13.0</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>642.0</v>
+        <v>643.0</v>
       </c>
       <c r="G118" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -571,7 +571,7 @@
         <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -649,7 +649,7 @@
         <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>134.0</v>
+        <v>137.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -707,7 +707,7 @@
         <v>122.0</v>
       </c>
       <c r="H18" t="n">
-        <v>423.0</v>
+        <v>424.0</v>
       </c>
     </row>
     <row r="19">
@@ -987,7 +987,7 @@
         <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>1775.0</v>
+        <v>1779.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2258.0</v>
+        <v>2259.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1247,7 +1247,7 @@
         <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>1540.0</v>
+        <v>1550.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1273,7 +1273,7 @@
         <v>59</v>
       </c>
       <c r="F40" t="n">
-        <v>1263.0</v>
+        <v>1277.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1871,7 +1871,7 @@
         <v>59</v>
       </c>
       <c r="F63" t="n">
-        <v>309.0</v>
+        <v>313.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="61">
   <si>
     <t>Area</t>
   </si>
@@ -363,13 +363,13 @@
         <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>333.0</v>
+        <v>338.0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -389,7 +389,7 @@
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>822.0</v>
+        <v>727.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -415,7 +415,7 @@
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>1401.0</v>
+        <v>1425.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -441,13 +441,13 @@
         <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>783.0</v>
+        <v>481.0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H8" t="n">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="9">
@@ -467,7 +467,7 @@
         <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>1498.0</v>
+        <v>1492.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -493,7 +493,7 @@
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>1962.0</v>
+        <v>1967.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -519,7 +519,7 @@
         <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>716.0</v>
+        <v>725.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -623,7 +623,7 @@
         <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>537.0</v>
+        <v>261.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -727,10 +727,10 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>1777.0</v>
+        <v>1726.0</v>
       </c>
       <c r="G19" t="n">
-        <v>56.0</v>
+        <v>55.0</v>
       </c>
       <c r="H19" t="n">
         <v>237.0</v>
@@ -805,7 +805,7 @@
         <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11331.0</v>
+        <v>11361.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3784.0</v>
+        <v>3791.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -857,7 +857,7 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7204.0</v>
+        <v>7237.0</v>
       </c>
       <c r="G24" t="n">
         <v>46.0</v>
@@ -883,13 +883,13 @@
         <v>59</v>
       </c>
       <c r="F25" t="n">
-        <v>3679.0</v>
+        <v>3332.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
       </c>
       <c r="H25" t="n">
-        <v>209.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="26">
@@ -909,13 +909,13 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8892.0</v>
+        <v>8853.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
       </c>
       <c r="H26" t="n">
-        <v>716.0</v>
+        <v>714.0</v>
       </c>
     </row>
     <row r="27">
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3616.0</v>
+        <v>3625.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5524.0</v>
+        <v>5551.0</v>
       </c>
       <c r="G28" t="n">
         <v>45.0</v>
@@ -1065,7 +1065,7 @@
         <v>59</v>
       </c>
       <c r="F32" t="n">
-        <v>6.0</v>
+        <v>282.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1371,19 +1371,19 @@
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
         <v>59</v>
       </c>
       <c r="F44" t="n">
-        <v>127.0</v>
+        <v>46.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="45">
@@ -1394,16 +1394,16 @@
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E45" t="s">
         <v>59</v>
       </c>
       <c r="F45" t="n">
-        <v>1.0</v>
+        <v>222.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1423,16 +1423,16 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E46" t="s">
         <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>753.0</v>
+        <v>1.0</v>
       </c>
       <c r="G46" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1446,19 +1446,19 @@
         <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E47" t="s">
         <v>59</v>
       </c>
       <c r="F47" t="n">
-        <v>1.0</v>
+        <v>753.0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1475,13 +1475,13 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E48" t="s">
         <v>59</v>
       </c>
       <c r="F48" t="n">
-        <v>174.0</v>
+        <v>1.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
@@ -1501,16 +1501,16 @@
         <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
         <v>59</v>
       </c>
       <c r="F49" t="n">
-        <v>86.0</v>
+        <v>174.0</v>
       </c>
       <c r="G49" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1527,19 +1527,19 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E50" t="s">
         <v>59</v>
       </c>
       <c r="F50" t="n">
-        <v>717.0</v>
+        <v>86.0</v>
       </c>
       <c r="G50" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H50" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -1553,19 +1553,19 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E51" t="s">
         <v>59</v>
       </c>
       <c r="F51" t="n">
-        <v>1636.0</v>
+        <v>717.0</v>
       </c>
       <c r="G51" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="H51" t="n">
-        <v>86.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="52">
@@ -1579,19 +1579,19 @@
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E52" t="s">
         <v>59</v>
       </c>
       <c r="F52" t="n">
-        <v>775.0</v>
+        <v>2285.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="53">
@@ -1602,22 +1602,22 @@
         <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E53" t="s">
         <v>59</v>
       </c>
       <c r="F53" t="n">
-        <v>1866.0</v>
+        <v>775.0</v>
       </c>
       <c r="G53" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -1631,19 +1631,19 @@
         <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E54" t="s">
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1831.0</v>
+        <v>1920.0</v>
       </c>
       <c r="G54" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="55">
@@ -1657,16 +1657,16 @@
         <v>16</v>
       </c>
       <c r="D55" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E55" t="s">
         <v>59</v>
       </c>
       <c r="F55" t="n">
+        <v>1840.0</v>
+      </c>
+      <c r="G55" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1683,16 +1683,16 @@
         <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E56" t="s">
         <v>59</v>
       </c>
       <c r="F56" t="n">
-        <v>1479.0</v>
+        <v>2.0</v>
       </c>
       <c r="G56" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H56" t="n">
         <v>0.0</v>
@@ -1709,19 +1709,19 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E57" t="s">
         <v>59</v>
       </c>
       <c r="F57" t="n">
-        <v>2842.0</v>
+        <v>1504.0</v>
       </c>
       <c r="G57" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H57" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -1735,19 +1735,19 @@
         <v>16</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E58" t="s">
         <v>59</v>
       </c>
       <c r="F58" t="n">
-        <v>2.0</v>
+        <v>2842.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="59">
@@ -1761,16 +1761,16 @@
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E59" t="s">
         <v>59</v>
       </c>
       <c r="F59" t="n">
-        <v>1596.0</v>
+        <v>2.0</v>
       </c>
       <c r="G59" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H59" t="n">
         <v>0.0</v>
@@ -1784,19 +1784,19 @@
         <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E60" t="s">
         <v>59</v>
       </c>
       <c r="F60" t="n">
+        <v>1599.0</v>
+      </c>
+      <c r="G60" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1813,13 +1813,13 @@
         <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E61" t="s">
         <v>59</v>
       </c>
       <c r="F61" t="n">
-        <v>949.0</v>
+        <v>2.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
@@ -1839,13 +1839,13 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E62" t="s">
         <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>1.0</v>
+        <v>949.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1865,13 +1865,13 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E63" t="s">
         <v>59</v>
       </c>
       <c r="F63" t="n">
-        <v>313.0</v>
+        <v>1.0</v>
       </c>
       <c r="G63" t="n">
         <v>0.0</v>
@@ -1891,13 +1891,13 @@
         <v>17</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E64" t="s">
         <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>37.0</v>
+        <v>313.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1917,13 +1917,13 @@
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E65" t="s">
         <v>59</v>
       </c>
       <c r="F65" t="n">
-        <v>1.0</v>
+        <v>37.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -1937,19 +1937,19 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="E66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F66" t="n">
-        <v>38.0</v>
+        <v>1.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1969,13 +1969,13 @@
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E67" t="s">
         <v>60</v>
       </c>
       <c r="F67" t="n">
-        <v>363.0</v>
+        <v>38.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1995,13 +1995,13 @@
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E68" t="s">
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>2441.0</v>
+        <v>363.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2021,13 +2021,13 @@
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E69" t="s">
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>669.0</v>
+        <v>2441.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2047,13 +2047,13 @@
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E70" t="s">
         <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>210.0</v>
+        <v>510.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2070,16 +2070,16 @@
         <v>9</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E71" t="s">
         <v>60</v>
       </c>
       <c r="F71" t="n">
-        <v>9.0</v>
+        <v>163.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2096,16 +2096,16 @@
         <v>9</v>
       </c>
       <c r="C72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E72" t="s">
         <v>60</v>
       </c>
       <c r="F72" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2131,13 +2131,13 @@
         <v>60</v>
       </c>
       <c r="F73" t="n">
-        <v>2341.0</v>
+        <v>66.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>12778.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1248.0</v>
+        <v>1251.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2287,7 +2287,7 @@
         <v>60</v>
       </c>
       <c r="F79" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2417,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="F84" t="n">
-        <v>4699.0</v>
+        <v>4698.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2573,7 +2573,7 @@
         <v>60</v>
       </c>
       <c r="F90" t="n">
-        <v>74.0</v>
+        <v>11.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2651,7 +2651,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>381.0</v>
+        <v>382.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -2717,19 +2717,19 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E96" t="s">
         <v>60</v>
       </c>
       <c r="F96" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G96" t="n">
         <v>0.0</v>
@@ -2749,13 +2749,13 @@
         <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E97" t="s">
         <v>60</v>
       </c>
       <c r="F97" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G97" t="n">
         <v>0.0</v>
@@ -2772,16 +2772,16 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E98" t="s">
         <v>60</v>
       </c>
       <c r="F98" t="n">
-        <v>7.0</v>
+        <v>16.0</v>
       </c>
       <c r="G98" t="n">
         <v>0.0</v>
@@ -2801,19 +2801,19 @@
         <v>17</v>
       </c>
       <c r="D99" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E99" t="s">
         <v>60</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
       </c>
       <c r="H99" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -2827,19 +2827,19 @@
         <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E100" t="s">
         <v>60</v>
       </c>
       <c r="F100" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="101">
@@ -2853,19 +2853,19 @@
         <v>17</v>
       </c>
       <c r="D101" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E101" t="s">
         <v>60</v>
       </c>
       <c r="F101" t="n">
-        <v>43.0</v>
+        <v>9.0</v>
       </c>
       <c r="G101" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H101" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -2873,25 +2873,25 @@
         <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="E102" t="s">
         <v>60</v>
       </c>
       <c r="F102" t="n">
-        <v>13.0</v>
+        <v>43.0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="103">
@@ -2902,16 +2902,16 @@
         <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E103" t="s">
         <v>60</v>
       </c>
       <c r="F103" t="n">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
@@ -2928,16 +2928,16 @@
         <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E104" t="s">
         <v>60</v>
       </c>
       <c r="F104" t="n">
-        <v>244.0</v>
+        <v>3.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2957,13 +2957,13 @@
         <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E105" t="s">
         <v>60</v>
       </c>
       <c r="F105" t="n">
-        <v>542.0</v>
+        <v>244.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2983,13 +2983,13 @@
         <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E106" t="s">
         <v>60</v>
       </c>
       <c r="F106" t="n">
-        <v>296.0</v>
+        <v>542.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -3009,13 +3009,13 @@
         <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E107" t="s">
         <v>60</v>
       </c>
       <c r="F107" t="n">
-        <v>1.0</v>
+        <v>296.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3035,13 +3035,13 @@
         <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E108" t="s">
         <v>60</v>
       </c>
       <c r="F108" t="n">
-        <v>306.0</v>
+        <v>161.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3058,16 +3058,16 @@
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E109" t="s">
         <v>60</v>
       </c>
       <c r="F109" t="n">
-        <v>13.0</v>
+        <v>353.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3084,16 +3084,16 @@
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E110" t="s">
         <v>60</v>
       </c>
       <c r="F110" t="n">
-        <v>4013.0</v>
+        <v>13.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3113,19 +3113,19 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E111" t="s">
         <v>60</v>
       </c>
       <c r="F111" t="n">
-        <v>7966.0</v>
+        <v>4013.0</v>
       </c>
       <c r="G111" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H111" t="n">
-        <v>16913.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="112">
@@ -3139,19 +3139,19 @@
         <v>15</v>
       </c>
       <c r="D112" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E112" t="s">
         <v>60</v>
       </c>
       <c r="F112" t="n">
-        <v>1229.0</v>
+        <v>7967.0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H112" t="n">
-        <v>670.0</v>
+        <v>16913.0</v>
       </c>
     </row>
     <row r="113">
@@ -3165,19 +3165,19 @@
         <v>15</v>
       </c>
       <c r="D113" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E113" t="s">
         <v>60</v>
       </c>
       <c r="F113" t="n">
-        <v>3880.0</v>
+        <v>1229.0</v>
       </c>
       <c r="G113" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H113" t="n">
-        <v>23.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="114">
@@ -3191,19 +3191,19 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E114" t="s">
         <v>60</v>
       </c>
       <c r="F114" t="n">
-        <v>79.0</v>
+        <v>6218.0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H114" t="n">
-        <v>0.0</v>
+        <v>12801.0</v>
       </c>
     </row>
     <row r="115">
@@ -3214,22 +3214,22 @@
         <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D115" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E115" t="s">
         <v>60</v>
       </c>
       <c r="F115" t="n">
-        <v>343.0</v>
+        <v>79.0</v>
       </c>
       <c r="G115" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H115" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="116">
@@ -3243,19 +3243,19 @@
         <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E116" t="s">
         <v>60</v>
       </c>
       <c r="F116" t="n">
-        <v>153.0</v>
+        <v>343.0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H116" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="117">
@@ -3269,16 +3269,16 @@
         <v>16</v>
       </c>
       <c r="D117" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E117" t="s">
         <v>60</v>
       </c>
       <c r="F117" t="n">
-        <v>13497.0</v>
+        <v>153.0</v>
       </c>
       <c r="G117" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H117" t="n">
         <v>0.0</v>
@@ -3295,19 +3295,19 @@
         <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E118" t="s">
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>643.0</v>
+        <v>13504.0</v>
       </c>
       <c r="G118" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="H118" t="n">
-        <v>66.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="119">
@@ -3321,19 +3321,19 @@
         <v>16</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E119" t="s">
         <v>60</v>
       </c>
       <c r="F119" t="n">
-        <v>4.0</v>
+        <v>643.0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H119" t="n">
-        <v>0.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="120">
@@ -3347,19 +3347,19 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E120" t="s">
         <v>60</v>
       </c>
       <c r="F120" t="n">
-        <v>1198.0</v>
+        <v>4.0</v>
       </c>
       <c r="G120" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H120" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="121">
@@ -3370,22 +3370,22 @@
         <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E121" t="s">
         <v>60</v>
       </c>
       <c r="F121" t="n">
+        <v>1198.0</v>
+      </c>
+      <c r="G121" t="n">
         <v>1.0</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H121" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="122">
@@ -3396,16 +3396,16 @@
         <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E122" t="s">
         <v>60</v>
       </c>
       <c r="F122" t="n">
-        <v>149.0</v>
+        <v>1.0</v>
       </c>
       <c r="G122" t="n">
         <v>0.0</v>
@@ -3425,13 +3425,13 @@
         <v>17</v>
       </c>
       <c r="D123" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E123" t="s">
         <v>60</v>
       </c>
       <c r="F123" t="n">
-        <v>1.0</v>
+        <v>149.0</v>
       </c>
       <c r="G123" t="n">
         <v>0.0</v>
@@ -3451,13 +3451,13 @@
         <v>17</v>
       </c>
       <c r="D124" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E124" t="s">
         <v>60</v>
       </c>
       <c r="F124" t="n">
-        <v>53.0</v>
+        <v>1.0</v>
       </c>
       <c r="G124" t="n">
         <v>0.0</v>
@@ -3474,21 +3474,47 @@
         <v>12</v>
       </c>
       <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>34</v>
+      </c>
+      <c r="E125" t="s">
+        <v>60</v>
+      </c>
+      <c r="F125" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>8</v>
+      </c>
+      <c r="B126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" t="s">
         <v>21</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D126" t="s">
         <v>58</v>
       </c>
-      <c r="E125" t="s">
-        <v>60</v>
-      </c>
-      <c r="F125" t="n">
+      <c r="E126" t="s">
+        <v>60</v>
+      </c>
+      <c r="F126" t="n">
         <v>5.0</v>
       </c>
-      <c r="G125" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H125" t="n">
+      <c r="G126" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H126" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -285,7 +285,7 @@
         <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>174.0</v>
+        <v>196.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -311,7 +311,7 @@
         <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>404.0</v>
+        <v>426.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -337,7 +337,7 @@
         <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="G4" t="n">
         <v>1.0</v>
@@ -363,7 +363,7 @@
         <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>338.0</v>
+        <v>343.0</v>
       </c>
       <c r="G5" t="n">
         <v>2.0</v>
@@ -389,7 +389,7 @@
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>727.0</v>
+        <v>729.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -675,13 +675,13 @@
         <v>59</v>
       </c>
       <c r="F17" t="n">
-        <v>513.0</v>
+        <v>518.0</v>
       </c>
       <c r="G17" t="n">
         <v>15.0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="18">
@@ -701,10 +701,10 @@
         <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>3978.0</v>
+        <v>3996.0</v>
       </c>
       <c r="G18" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="H18" t="n">
         <v>424.0</v>
@@ -727,7 +727,7 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>1726.0</v>
+        <v>1764.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -779,7 +779,7 @@
         <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>723.0</v>
+        <v>739.0</v>
       </c>
       <c r="G21" t="n">
         <v>22.0</v>
@@ -805,7 +805,7 @@
         <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11361.0</v>
+        <v>11366.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3791.0</v>
+        <v>3796.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -857,13 +857,13 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7237.0</v>
+        <v>7254.0</v>
       </c>
       <c r="G24" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="H24" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
     </row>
     <row r="25">
@@ -883,7 +883,7 @@
         <v>59</v>
       </c>
       <c r="F25" t="n">
-        <v>3332.0</v>
+        <v>3348.0</v>
       </c>
       <c r="G25" t="n">
         <v>7.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8853.0</v>
+        <v>8879.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3625.0</v>
+        <v>3627.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,10 +961,10 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5551.0</v>
+        <v>5557.0</v>
       </c>
       <c r="G28" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="H28" t="n">
         <v>20.0</v>
@@ -1094,7 +1094,7 @@
         <v>143.0</v>
       </c>
       <c r="G33" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H33" t="n">
         <v>2.0</v>
@@ -1299,7 +1299,7 @@
         <v>59</v>
       </c>
       <c r="F41" t="n">
-        <v>729.0</v>
+        <v>808.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1325,7 +1325,7 @@
         <v>59</v>
       </c>
       <c r="F42" t="n">
-        <v>490.0</v>
+        <v>524.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1351,7 +1351,7 @@
         <v>59</v>
       </c>
       <c r="F43" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1403,7 +1403,7 @@
         <v>59</v>
       </c>
       <c r="F45" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1455,7 +1455,7 @@
         <v>59</v>
       </c>
       <c r="F47" t="n">
-        <v>753.0</v>
+        <v>775.0</v>
       </c>
       <c r="G47" t="n">
         <v>3.0</v>
@@ -1507,7 +1507,7 @@
         <v>59</v>
       </c>
       <c r="F49" t="n">
-        <v>174.0</v>
+        <v>175.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1559,7 +1559,7 @@
         <v>59</v>
       </c>
       <c r="F51" t="n">
-        <v>717.0</v>
+        <v>719.0</v>
       </c>
       <c r="G51" t="n">
         <v>3.0</v>
@@ -1585,7 +1585,7 @@
         <v>59</v>
       </c>
       <c r="F52" t="n">
-        <v>2285.0</v>
+        <v>2288.0</v>
       </c>
       <c r="G52" t="n">
         <v>6.0</v>
@@ -1637,7 +1637,7 @@
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1920.0</v>
+        <v>1921.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1715,7 +1715,7 @@
         <v>59</v>
       </c>
       <c r="F57" t="n">
-        <v>1504.0</v>
+        <v>1506.0</v>
       </c>
       <c r="G57" t="n">
         <v>6.0</v>
@@ -1845,7 +1845,7 @@
         <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>949.0</v>
+        <v>959.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -2001,7 +2001,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>363.0</v>
+        <v>365.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2027,7 +2027,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>2441.0</v>
+        <v>2460.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2053,7 +2053,7 @@
         <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>510.0</v>
+        <v>514.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2079,7 +2079,7 @@
         <v>60</v>
       </c>
       <c r="F71" t="n">
-        <v>163.0</v>
+        <v>171.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1251.0</v>
+        <v>1257.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2365,7 +2365,7 @@
         <v>60</v>
       </c>
       <c r="F82" t="n">
-        <v>108.0</v>
+        <v>110.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2391,7 +2391,7 @@
         <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>3073.0</v>
+        <v>3091.0</v>
       </c>
       <c r="G83" t="n">
         <v>2.0</v>
@@ -2417,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="F84" t="n">
-        <v>4698.0</v>
+        <v>4709.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2599,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>263.0</v>
+        <v>264.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2651,7 +2651,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>382.0</v>
+        <v>383.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -3067,7 +3067,7 @@
         <v>60</v>
       </c>
       <c r="F109" t="n">
-        <v>353.0</v>
+        <v>358.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3119,7 +3119,7 @@
         <v>60</v>
       </c>
       <c r="F111" t="n">
-        <v>4013.0</v>
+        <v>4014.0</v>
       </c>
       <c r="G111" t="n">
         <v>0.0</v>
@@ -3145,7 +3145,7 @@
         <v>60</v>
       </c>
       <c r="F112" t="n">
-        <v>7967.0</v>
+        <v>7968.0</v>
       </c>
       <c r="G112" t="n">
         <v>1.0</v>
@@ -3197,7 +3197,7 @@
         <v>60</v>
       </c>
       <c r="F114" t="n">
-        <v>6218.0</v>
+        <v>6229.0</v>
       </c>
       <c r="G114" t="n">
         <v>1.0</v>
@@ -3249,7 +3249,7 @@
         <v>60</v>
       </c>
       <c r="F116" t="n">
-        <v>343.0</v>
+        <v>344.0</v>
       </c>
       <c r="G116" t="n">
         <v>1.0</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>13504.0</v>
+        <v>13513.0</v>
       </c>
       <c r="G118" t="n">
         <v>13.0</v>
@@ -3379,7 +3379,7 @@
         <v>60</v>
       </c>
       <c r="F121" t="n">
-        <v>1198.0</v>
+        <v>1200.0</v>
       </c>
       <c r="G121" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -415,7 +415,7 @@
         <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>1425.0</v>
+        <v>1466.0</v>
       </c>
       <c r="G7" t="n">
         <v>2.0</v>
@@ -493,7 +493,7 @@
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>1967.0</v>
+        <v>1980.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -519,7 +519,7 @@
         <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>725.0</v>
+        <v>744.0</v>
       </c>
       <c r="G11" t="n">
         <v>3.0</v>
@@ -623,7 +623,7 @@
         <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -649,7 +649,7 @@
         <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>137.0</v>
+        <v>151.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -805,7 +805,7 @@
         <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11366.0</v>
+        <v>11435.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3796.0</v>
+        <v>3854.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -857,10 +857,10 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7254.0</v>
+        <v>7332.0</v>
       </c>
       <c r="G24" t="n">
-        <v>48.0</v>
+        <v>51.0</v>
       </c>
       <c r="H24" t="n">
         <v>277.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8879.0</v>
+        <v>8888.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3627.0</v>
+        <v>3650.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5557.0</v>
+        <v>5616.0</v>
       </c>
       <c r="G28" t="n">
         <v>46.0</v>
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2259.0</v>
+        <v>2314.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1065,7 +1065,7 @@
         <v>59</v>
       </c>
       <c r="F32" t="n">
-        <v>282.0</v>
+        <v>288.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1247,7 +1247,7 @@
         <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>1550.0</v>
+        <v>1574.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1273,7 +1273,7 @@
         <v>59</v>
       </c>
       <c r="F40" t="n">
-        <v>1277.0</v>
+        <v>1282.0</v>
       </c>
       <c r="G40" t="n">
         <v>1.0</v>
@@ -1637,7 +1637,7 @@
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1921.0</v>
+        <v>1923.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1663,7 +1663,7 @@
         <v>59</v>
       </c>
       <c r="F55" t="n">
-        <v>1840.0</v>
+        <v>1844.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1715,7 +1715,7 @@
         <v>59</v>
       </c>
       <c r="F57" t="n">
-        <v>1506.0</v>
+        <v>1516.0</v>
       </c>
       <c r="G57" t="n">
         <v>6.0</v>
@@ -1845,7 +1845,7 @@
         <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>959.0</v>
+        <v>1031.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1897,7 +1897,7 @@
         <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>313.0</v>
+        <v>315.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1923,7 +1923,7 @@
         <v>59</v>
       </c>
       <c r="F65" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="G65" t="n">
         <v>0.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1257.0</v>
+        <v>1258.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2651,7 +2651,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>383.0</v>
+        <v>384.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>13513.0</v>
+        <v>13514.0</v>
       </c>
       <c r="G118" t="n">
         <v>13.0</v>
@@ -3379,7 +3379,7 @@
         <v>60</v>
       </c>
       <c r="F121" t="n">
-        <v>1200.0</v>
+        <v>1206.0</v>
       </c>
       <c r="G121" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -285,7 +285,7 @@
         <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>196.0</v>
+        <v>198.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -311,7 +311,7 @@
         <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>426.0</v>
+        <v>430.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -389,7 +389,7 @@
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>729.0</v>
+        <v>737.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -493,7 +493,7 @@
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>1980.0</v>
+        <v>1995.0</v>
       </c>
       <c r="G10" t="n">
         <v>4.0</v>
@@ -701,7 +701,7 @@
         <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>3996.0</v>
+        <v>4000.0</v>
       </c>
       <c r="G18" t="n">
         <v>123.0</v>
@@ -727,7 +727,7 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>1764.0</v>
+        <v>1765.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -805,7 +805,7 @@
         <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11435.0</v>
+        <v>11438.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3854.0</v>
+        <v>3862.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -857,7 +857,7 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7332.0</v>
+        <v>7333.0</v>
       </c>
       <c r="G24" t="n">
         <v>51.0</v>
@@ -909,7 +909,7 @@
         <v>59</v>
       </c>
       <c r="F26" t="n">
-        <v>8888.0</v>
+        <v>8915.0</v>
       </c>
       <c r="G26" t="n">
         <v>21.0</v>
@@ -935,7 +935,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="n">
-        <v>3650.0</v>
+        <v>3660.0</v>
       </c>
       <c r="G27" t="n">
         <v>7.0</v>
@@ -961,13 +961,13 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5616.0</v>
+        <v>5622.0</v>
       </c>
       <c r="G28" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="H28" t="n">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="29">
@@ -987,7 +987,7 @@
         <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>1779.0</v>
+        <v>1805.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1299,7 +1299,7 @@
         <v>59</v>
       </c>
       <c r="F41" t="n">
-        <v>808.0</v>
+        <v>829.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1403,7 +1403,7 @@
         <v>59</v>
       </c>
       <c r="F45" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1455,7 +1455,7 @@
         <v>59</v>
       </c>
       <c r="F47" t="n">
-        <v>775.0</v>
+        <v>799.0</v>
       </c>
       <c r="G47" t="n">
         <v>3.0</v>
@@ -1637,7 +1637,7 @@
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1923.0</v>
+        <v>1926.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1663,7 +1663,7 @@
         <v>59</v>
       </c>
       <c r="F55" t="n">
-        <v>1844.0</v>
+        <v>1861.0</v>
       </c>
       <c r="G55" t="n">
         <v>2.0</v>
@@ -1715,7 +1715,7 @@
         <v>59</v>
       </c>
       <c r="F57" t="n">
-        <v>1516.0</v>
+        <v>1531.0</v>
       </c>
       <c r="G57" t="n">
         <v>6.0</v>
@@ -1793,7 +1793,7 @@
         <v>59</v>
       </c>
       <c r="F60" t="n">
-        <v>1599.0</v>
+        <v>1600.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -1845,7 +1845,7 @@
         <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>1031.0</v>
+        <v>1076.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1897,7 +1897,7 @@
         <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>315.0</v>
+        <v>325.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -1975,7 +1975,7 @@
         <v>60</v>
       </c>
       <c r="F67" t="n">
-        <v>38.0</v>
+        <v>42.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2001,7 +2001,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>365.0</v>
+        <v>370.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2027,7 +2027,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>2460.0</v>
+        <v>2466.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2053,7 +2053,7 @@
         <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>514.0</v>
+        <v>519.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2079,7 +2079,7 @@
         <v>60</v>
       </c>
       <c r="F71" t="n">
-        <v>171.0</v>
+        <v>175.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2391,7 +2391,7 @@
         <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>3091.0</v>
+        <v>3095.0</v>
       </c>
       <c r="G83" t="n">
         <v>2.0</v>
@@ -2417,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="F84" t="n">
-        <v>4709.0</v>
+        <v>4728.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2443,7 +2443,7 @@
         <v>60</v>
       </c>
       <c r="F85" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2599,7 +2599,7 @@
         <v>60</v>
       </c>
       <c r="F91" t="n">
-        <v>264.0</v>
+        <v>265.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2963,7 +2963,7 @@
         <v>60</v>
       </c>
       <c r="F105" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2989,7 +2989,7 @@
         <v>60</v>
       </c>
       <c r="F106" t="n">
-        <v>542.0</v>
+        <v>543.0</v>
       </c>
       <c r="G106" t="n">
         <v>0.0</v>
@@ -3015,7 +3015,7 @@
         <v>60</v>
       </c>
       <c r="F107" t="n">
-        <v>296.0</v>
+        <v>297.0</v>
       </c>
       <c r="G107" t="n">
         <v>0.0</v>
@@ -3041,7 +3041,7 @@
         <v>60</v>
       </c>
       <c r="F108" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>13514.0</v>
+        <v>13526.0</v>
       </c>
       <c r="G118" t="n">
         <v>13.0</v>
@@ -3379,7 +3379,7 @@
         <v>60</v>
       </c>
       <c r="F121" t="n">
-        <v>1206.0</v>
+        <v>1208.0</v>
       </c>
       <c r="G121" t="n">
         <v>1.0</v>

--- a/Download/CasiControlli_ZR.xlsx
+++ b/Download/CasiControlli_ZR.xlsx
@@ -389,7 +389,7 @@
         <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>737.0</v>
+        <v>739.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -571,7 +571,7 @@
         <v>59</v>
       </c>
       <c r="F13" t="n">
-        <v>195.0</v>
+        <v>197.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -649,7 +649,7 @@
         <v>59</v>
       </c>
       <c r="F16" t="n">
-        <v>151.0</v>
+        <v>159.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -707,7 +707,7 @@
         <v>123.0</v>
       </c>
       <c r="H18" t="n">
-        <v>424.0</v>
+        <v>425.0</v>
       </c>
     </row>
     <row r="19">
@@ -727,7 +727,7 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>1765.0</v>
+        <v>1766.0</v>
       </c>
       <c r="G19" t="n">
         <v>55.0</v>
@@ -805,7 +805,7 @@
         <v>59</v>
       </c>
       <c r="F22" t="n">
-        <v>11438.0</v>
+        <v>11449.0</v>
       </c>
       <c r="G22" t="n">
         <v>147.0</v>
@@ -831,7 +831,7 @@
         <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>3862.0</v>
+        <v>3871.0</v>
       </c>
       <c r="G23" t="n">
         <v>21.0</v>
@@ -857,10 +857,10 @@
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>7333.0</v>
+        <v>7337.0</v>
       </c>
       <c r="G24" t="n">
-        <v>51.0</v>
+        <v>54.0</v>
       </c>
       <c r="H24" t="n">
         <v>277.0</v>
@@ -961,7 +961,7 @@
         <v>59</v>
       </c>
       <c r="F28" t="n">
-        <v>5622.0</v>
+        <v>5623.0</v>
       </c>
       <c r="G28" t="n">
         <v>47.0</v>
@@ -987,7 +987,7 @@
         <v>59</v>
       </c>
       <c r="F29" t="n">
-        <v>1805.0</v>
+        <v>1808.0</v>
       </c>
       <c r="G29" t="n">
         <v>1.0</v>
@@ -1039,7 +1039,7 @@
         <v>59</v>
       </c>
       <c r="F31" t="n">
-        <v>2314.0</v>
+        <v>2339.0</v>
       </c>
       <c r="G31" t="n">
         <v>1.0</v>
@@ -1247,7 +1247,7 @@
         <v>59</v>
       </c>
       <c r="F39" t="n">
-        <v>1574.0</v>
+        <v>1584.0</v>
       </c>
       <c r="G39" t="n">
         <v>2.0</v>
@@ -1637,7 +1637,7 @@
         <v>59</v>
       </c>
       <c r="F54" t="n">
-        <v>1926.0</v>
+        <v>1927.0</v>
       </c>
       <c r="G54" t="n">
         <v>4.0</v>
@@ -1715,7 +1715,7 @@
         <v>59</v>
       </c>
       <c r="F57" t="n">
-        <v>1531.0</v>
+        <v>1543.0</v>
       </c>
       <c r="G57" t="n">
         <v>6.0</v>
@@ -1845,7 +1845,7 @@
         <v>59</v>
       </c>
       <c r="F62" t="n">
-        <v>1076.0</v>
+        <v>1115.0</v>
       </c>
       <c r="G62" t="n">
         <v>0.0</v>
@@ -1897,7 +1897,7 @@
         <v>59</v>
       </c>
       <c r="F64" t="n">
-        <v>325.0</v>
+        <v>327.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
@@ -2001,7 +2001,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>370.0</v>
+        <v>373.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2027,7 +2027,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>2466.0</v>
+        <v>2467.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2079,7 +2079,7 @@
         <v>60</v>
       </c>
       <c r="F71" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
@@ -2209,7 +2209,7 @@
         <v>60</v>
       </c>
       <c r="F76" t="n">
-        <v>1258.0</v>
+        <v>1265.0</v>
       </c>
       <c r="G76" t="n">
         <v>1.0</v>
@@ -2391,7 +2391,7 @@
         <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>3095.0</v>
+        <v>3105.0</v>
       </c>
       <c r="G83" t="n">
         <v>2.0</v>
@@ -2417,7 +2417,7 @@
         <v>60</v>
       </c>
       <c r="F84" t="n">
-        <v>4728.0</v>
+        <v>4736.0</v>
       </c>
       <c r="G84" t="n">
         <v>0.0</v>
@@ -2651,7 +2651,7 @@
         <v>60</v>
       </c>
       <c r="F93" t="n">
-        <v>384.0</v>
+        <v>386.0</v>
       </c>
       <c r="G93" t="n">
         <v>1.0</v>
@@ -3093,7 +3093,7 @@
         <v>60</v>
       </c>
       <c r="F110" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3301,7 +3301,7 @@
         <v>60</v>
       </c>
       <c r="F118" t="n">
-        <v>13526.0</v>
+        <v>13552.0</v>
       </c>
       <c r="G118" t="n">
         <v>13.0</v>
@@ -3327,7 +3327,7 @@
         <v>60</v>
       </c>
       <c r="F119" t="n">
-        <v>643.0</v>
+        <v>644.0</v>
       </c>
       <c r="G119" t="n">
         <v>1.0</v>
@@ -3379,7 +3379,7 @@
         <v>60</v>
       </c>
       <c r="F121" t="n">
-        <v>1208.0</v>
+        <v>1211.0</v>
       </c>
       <c r="G121" t="n">
         <v>1.0</v>
